--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -1870,7 +1870,7 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Rule: Saving Max = second highest saving rate, excluding the first highest. See the Notes sheet for assumptions and missing values.</t>
+          <t>Rule: Saving Max = second highest saving rate, excluding the first highest. See the Notes sheet for assumptions and missing values. Newer notices not yet extracted: EBL.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interest Rate Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$J$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$AB$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly History'!$A$1:$N$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,7 +53,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +68,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0019376D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0024477F"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -114,30 +121,33 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,6 +158,51 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -509,29 +564,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank Deposit Interest Rate Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Bank Deposit Interest Rates — Ashwin 2083 vs Bhadra 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Bank</t>
@@ -543,1354 +616,6523 @@
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Call</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Individual FD</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Institution FD</t>
+          <t>Call</t>
         </is>
       </c>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Individual FD</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>Institution FD</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
+      <c r="X3" s="2" t="n"/>
+      <c r="Y3" s="2" t="n"/>
+      <c r="Z3" s="2" t="n"/>
+      <c r="AA3" s="2" t="n"/>
+      <c r="AB3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Min Ashwin 2083</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
+          <t>Min Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Changes</t>
+        </is>
+      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Less Than 1 Year Max</t>
+          <t>Max Ashwin 2083</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>1 Year</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>More Than 1 Year Max</t>
+          <t>Max Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Changes</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Less Than 1 Year Max</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>1 Year</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>More Than 1 Year Max</t>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Changes</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Less Than 1 Year Max Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Less Than 1 Year Max Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Less Than 1 Year Max Changes</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>1 Year Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>1 Year Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>1 Year Changes</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>More Than 1 Year Max Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>More Than 1 Year Max Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>More Than 1 Year Max Changes</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Less Than 1 Year Max Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Less Than 1 Year Max Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Less Than 1 Year Max Changes</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>1 Year Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>1 Year Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>1 Year Changes</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>More Than 1 Year Max Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>More Than 1 Year Max Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>More Than 1 Year Max Changes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
+      <c r="AA5" s="6" t="n"/>
+      <c r="AB5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Corporate Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Up to 1.42%</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="U6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="X6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z6" s="8" t="n">
         <v>0.0475</v>
       </c>
+      <c r="AA6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C7" s="10" t="n">
+      <c r="B7" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
         <v>0.0375</v>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G7" s="10" t="n">
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q7" s="12" t="n">
         <v>0.0428</v>
       </c>
-      <c r="H7" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J7" s="10" t="n">
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W7" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z7" s="12" t="n">
         <v>0.0325</v>
       </c>
+      <c r="AA7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Green Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C8" s="7" t="n">
+      <c r="B8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>0.0525</v>
       </c>
-      <c r="H8" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I8" s="7" t="n">
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="X8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z8" s="8" t="n">
         <v>0.0425</v>
       </c>
+      <c r="AA8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G9" s="10" t="n">
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="n">
         <v>0.0428</v>
       </c>
-      <c r="H9" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.0275</v>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C10" s="7" t="n">
+      <c r="B10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G10" s="7" t="n">
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I10" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J10" s="7" t="n">
+      <c r="U10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z10" s="8" t="n">
         <v>0.0335</v>
       </c>
+      <c r="AA10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C11" s="10" t="n">
+      <c r="B11" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
         <v>0.028</v>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>0.028</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="n">
         <v>0.028</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="12" t="n">
         <v>0.045</v>
       </c>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="13" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I11" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J11" s="10" t="n">
+      <c r="U11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W11" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z11" s="12" t="n">
         <v>0.03</v>
       </c>
+      <c r="AA11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="B12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>As per NRB guidelines</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="n">
         <v>0.043</v>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J12" s="7" t="n">
+      <c r="U12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="n">
         <v>0.0425</v>
       </c>
+      <c r="AA12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C13" s="10" t="n">
+      <c r="B13" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>0.028</v>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>Up to 1.00%</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G13" s="10" t="n">
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="12" t="n">
         <v>0.0428</v>
       </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="13" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I13" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J13" s="10" t="n">
+      <c r="U13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W13" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z13" s="12" t="n">
         <v>0.032</v>
       </c>
+      <c r="AA13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Narayani Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="B14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>1.375%</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="n">
         <v>0.0495</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="n">
         <v>0.0515</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="n">
         <v>0.0515</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
         <v>0.0495</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="U14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="n">
         <v>0.0515</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="X14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="n">
         <v>0.0515</v>
       </c>
+      <c r="AA14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C15" s="10" t="n">
+      <c r="B15" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="n">
         <v>0.045</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="n">
         <v>0.05</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="O15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="12" t="n">
         <v>0.055</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="12" t="n">
         <v>0.04</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="U15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W15" s="12" t="n">
         <v>0.0425</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="X15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z15" s="12" t="n">
         <v>0.05</v>
       </c>
+      <c r="AA15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="B16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G16" s="7" t="n">
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="H16" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>0.0275</v>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C17" s="10" t="n">
+      <c r="B17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
         <v>0.0325</v>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F17" s="10" t="n">
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="n">
         <v>0.0325</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="O17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" s="12" t="n">
         <v>0.0459</v>
       </c>
-      <c r="H17" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J17" s="10" t="n">
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z17" s="12" t="n">
         <v>0.035</v>
       </c>
+      <c r="AA17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C18" s="7" t="n">
+      <c r="B18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F18" s="7" t="n">
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="n">
         <v>0.0394</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="H18" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>0.0275</v>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
+      <c r="T19" s="6" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
+      <c r="Z19" s="6" t="n"/>
+      <c r="AA19" s="6" t="n"/>
+      <c r="AB19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
         <v>0.0304</v>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>0.45%</t>
         </is>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>0.0415</v>
       </c>
-      <c r="H20" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>0.0275</v>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C21" s="10" t="n">
+      <c r="B21" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
         <v>0.028</v>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>Negotiable as per NRB Directive</t>
         </is>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="n">
         <v>0.0285</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="12" t="n">
         <v>0.029</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="n">
         <v>0.0385</v>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="13" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="U21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W21" s="13" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J21" s="10" t="n">
-        <v>0.0275</v>
+      <c r="X21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z21" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB21" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Everest Bank Ltd.</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="B22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Up to 0.50%</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G22" s="7" t="n">
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="H22" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J22" s="7" t="n">
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="n">
         <v>0.0325</v>
       </c>
+      <c r="AA22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Global IME Bank Ltd.</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>Up to 50% of minimum saving deposit rate</t>
         </is>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>0.0276</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="n">
         <v>0.0276</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q23" s="12" t="n">
         <v>0.04</v>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="R23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="13" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I23" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>0.0275</v>
+      <c r="U23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="U24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="X24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z24" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
+      <c r="AA24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Kumari Bank Ltd.</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C25" s="10" t="n">
+      <c r="B25" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
         <v>0.0391</v>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>Up to 0.81%</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G25" s="10" t="n">
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" s="12" t="n">
         <v>0.0343</v>
       </c>
-      <c r="H25" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J25" s="10" t="n">
+      <c r="R25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W25" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z25" s="12" t="n">
         <v>0.0301</v>
       </c>
+      <c r="AA25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C26" s="7" t="n">
+      <c r="B26" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Negotiable (max 50% of lowest saving rate)</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="H26" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J26" s="7" t="n">
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z26" s="8" t="n">
         <v>0.0325</v>
       </c>
+      <c r="AA26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C27" s="10" t="n">
+      <c r="B27" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
         <v>0.028</v>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>Up to 0.25%</t>
         </is>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="O27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q27" s="12" t="n">
         <v>0.045</v>
       </c>
-      <c r="H27" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J27" s="10" t="n">
+      <c r="R27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T27" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W27" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z27" s="12" t="n">
         <v>0.03</v>
       </c>
+      <c r="AA27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Nabil Bank Ltd.</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C28" s="7" t="n">
+      <c r="B28" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>As per agreement</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="O28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="H28" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J28" s="7" t="n">
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z28" s="8" t="n">
         <v>0.0301</v>
       </c>
+      <c r="AA28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Nepal Bank Ltd.</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="12" t="n">
         <v>0.0276</v>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
         <v>0.0301</v>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>0.20%</t>
         </is>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="n">
         <v>0.0276</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="n">
         <v>0.0276</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="O29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q29" s="12" t="n">
         <v>0.0415</v>
       </c>
-      <c r="H29" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J29" s="10" t="n">
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W29" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z29" s="12" t="n">
         <v>0.035</v>
       </c>
+      <c r="AA29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="B30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G30" s="7" t="n">
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="H30" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J30" s="7" t="n">
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z30" s="8" t="n">
         <v>0.03</v>
       </c>
+      <c r="AA30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C31" s="10" t="n">
+      <c r="B31" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
         <v>0.0375</v>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>Up to 1.35%</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="n">
         <v>0.029</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="O31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q31" s="12" t="n">
         <v>0.045</v>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T31" s="13" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I31" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J31" s="10" t="n">
+      <c r="U31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W31" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z31" s="12" t="n">
         <v>0.035</v>
       </c>
+      <c r="AA31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>NMB Bank Ltd.</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="B32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="E32" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G32" s="7" t="n">
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I32" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J32" s="7" t="n">
+      <c r="U32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z32" s="8" t="n">
         <v>0.035</v>
       </c>
+      <c r="AA32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
+      <c r="B33" s="12" t="n">
         <v>0.0276</v>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
         <v>0.0302</v>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="12" t="n">
         <v>0.029</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="O33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q33" s="12" t="n">
         <v>0.04</v>
       </c>
-      <c r="H33" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I33" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>0.0275</v>
+      <c r="R33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T33" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W33" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z33" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C34" s="7" t="n">
+      <c r="B34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Up to 0.10%</t>
         </is>
       </c>
-      <c r="E34" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G34" s="7" t="n">
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="n">
         <v>0.0455</v>
       </c>
-      <c r="H34" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J34" s="7" t="n">
-        <v>0.0275</v>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C35" s="10" t="n">
+      <c r="B35" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
         <v>0.028</v>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="E35" s="10" t="n">
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="F35" s="10" t="n">
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="12" t="n">
         <v>0.0315</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="O35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q35" s="12" t="n">
         <v>0.04</v>
       </c>
-      <c r="H35" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J35" s="10" t="n">
+      <c r="R35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W35" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z35" s="12" t="n">
         <v>0.03</v>
       </c>
+      <c r="AA35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB35" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Sanima Bank Ltd.</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C36" s="7" t="n">
+      <c r="B36" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="O36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="H36" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J36" s="7" t="n">
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z36" s="8" t="n">
         <v>0.0351</v>
       </c>
+      <c r="AA36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C37" s="10" t="n">
+      <c r="B37" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
         <v>0.0279</v>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>Up to 0.75%</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>0.032</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="O37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q37" s="12" t="n">
         <v>0.04099999999999999</v>
       </c>
-      <c r="H37" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I37" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>0.0275</v>
+      <c r="R37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W37" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z37" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C38" s="7" t="n">
+      <c r="B38" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>0.0305</v>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>Up to 0.25%</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G38" s="7" t="n">
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>0.03759999999999999</v>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T38" s="9" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I38" s="7" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J38" s="7" t="n">
+      <c r="U38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z38" s="8" t="n">
         <v>0.0305</v>
       </c>
+      <c r="AA38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Standard Chartered Bank Nepal Ltd.</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>Up to 0.20%</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G39" s="10" t="n">
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q39" s="12" t="n">
         <v>0.0375</v>
       </c>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="R39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T39" s="13" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I39" s="10" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>0.0275</v>
+      <c r="U39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W39" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z39" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>Rule: Saving Max = second highest saving rate, excluding the first highest. See the Notes sheet for assumptions and missing values.</t>
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J39"/>
+  <autoFilter ref="A4:AB39"/>
   <mergeCells count="8">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="A19:AB19"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A5:AB5"/>
+    <mergeCell ref="K3:S3"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="T3:AB3"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A19:J19"/>
   </mergeCells>
+  <conditionalFormatting sqref="D5:D39">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(D5),D5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>AND(ISNUMBER(D5),D5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>AND(ISNUMBER(D5),D5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>D5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G39">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>AND(ISNUMBER(G5),G5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>AND(ISNUMBER(G5),G5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>AND(ISNUMBER(G5),G5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="3">
+      <formula>G5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J39">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>AND(ISNUMBER(J5),J5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>AND(ISNUMBER(J5),J5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="2">
+      <formula>AND(ISNUMBER(J5),J5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="3">
+      <formula>J5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M39">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>AND(ISNUMBER(M5),M5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="1">
+      <formula>AND(ISNUMBER(M5),M5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="2">
+      <formula>AND(ISNUMBER(M5),M5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="3">
+      <formula>M5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P5:P39">
+    <cfRule type="expression" priority="17" dxfId="0">
+      <formula>AND(ISNUMBER(P5),P5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="1">
+      <formula>AND(ISNUMBER(P5),P5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="19" dxfId="2">
+      <formula>AND(ISNUMBER(P5),P5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="3">
+      <formula>P5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5:S39">
+    <cfRule type="expression" priority="21" dxfId="0">
+      <formula>AND(ISNUMBER(S5),S5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="22" dxfId="1">
+      <formula>AND(ISNUMBER(S5),S5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="23" dxfId="2">
+      <formula>AND(ISNUMBER(S5),S5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" dxfId="3">
+      <formula>S5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V5:V39">
+    <cfRule type="expression" priority="25" dxfId="0">
+      <formula>AND(ISNUMBER(V5),V5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="26" dxfId="1">
+      <formula>AND(ISNUMBER(V5),V5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" dxfId="2">
+      <formula>AND(ISNUMBER(V5),V5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="28" dxfId="3">
+      <formula>V5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y5:Y39">
+    <cfRule type="expression" priority="29" dxfId="0">
+      <formula>AND(ISNUMBER(Y5),Y5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="1">
+      <formula>AND(ISNUMBER(Y5),Y5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="31" dxfId="2">
+      <formula>AND(ISNUMBER(Y5),Y5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="32" dxfId="3">
+      <formula>Y5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB5:AB39">
+    <cfRule type="expression" priority="33" dxfId="0">
+      <formula>AND(ISNUMBER(AB5),AB5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="34" dxfId="1">
+      <formula>AND(ISNUMBER(AB5),AB5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="2">
+      <formula>AND(ISNUMBER(AB5),AB5=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="3">
+      <formula>AB5="Changed"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Fiscal Month #</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Saving Min</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Saving Max</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Individual FD &lt;1Y Max</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Individual FD 1Y</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Individual FD &gt;1Y Max</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Institution FD &lt;1Y Max</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Institution FD 1Y</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Institution FD &gt;1Y Max</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Effective Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Corporate Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.42%</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>1 Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Garima Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L3" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M3" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="N3" s="14" t="inlineStr">
+        <is>
+          <t>2083.06.01 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Green Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>1st Ashoj 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Jyoti Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Kamana Sewa Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Lumbini Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin month 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Mahalaxmi Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>As per NRB guidelines</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1st Aswin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Muktinath Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Up to 1.00%</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t>1st Ashoj 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Narayani Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>1.375%</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Salapa Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>Ashoj 01, 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Shangri-la Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Shine Resunga Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t>2083-06-01 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Sindhu Bikash Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>2083/06/01 (Nepali notice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Agricultural Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N15" s="14" t="inlineStr">
+        <is>
+          <t>Aswin 01, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Citizens Bank International Ltd.</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Negotiable as per NRB Directive</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>1 Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Everest Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Up to 0.50%</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1 Ashoj 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Global IME Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Up to 50% of minimum saving deposit rate</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Himalayan Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Kumari Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.81%</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>01 Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Laxmi Sunrise Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Negotiable (max 50% of lowest saving rate)</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="N21" s="14" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Machhapuchchhre Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.25%</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>NIC Asia Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>NMB Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>Asoj 1, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Nabil Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>As per agreement</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="N25" s="14" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1 Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Nepal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>1st Ashwin 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Up to 1.35%</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N27" s="14" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Nepal SBI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.75%</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Prabhu Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Up to 0.10%</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (01 Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>01st Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Rastriya Banijya Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>2083 Asoj 01 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Sanima Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 1, 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Siddhartha Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Up to 0.25%</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="N33" s="14" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Ltd.</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.20%</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N34"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1929,47 +7171,47 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Notes / Assumptions</t>
+          <t>Notes (Ashwin 2083)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>All banks</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr"/>
-      <c r="C2" s="15" t="inlineStr"/>
-      <c r="D2" s="15" t="inlineStr"/>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>Saving Max is the second highest saving rate, excluding the first highest. Call and FCY accounts are excluded from saving rates; loan, base and spread rates are excluded. Remittance FD rates are excluded from Individual FD.</t>
+      <c r="B2" s="16" t="inlineStr"/>
+      <c r="C2" s="16" t="inlineStr"/>
+      <c r="D2" s="16" t="inlineStr"/>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>Saving Max is the second highest saving rate, excluding the first highest. Call and FCY accounts are excluded from saving rates; loan, base and spread rates are excluded. Remittance FD rates are excluded from Individual FD. Months follow the Nepali calendar (Shrawan to Ashadh).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Corporate Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67425</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>• Individual FD: 3M 3.50%, 6-9M 3.75%, 1Y 4.25%, &gt;1-2Y 4.50%, &gt;2-3Y 5.00%, &gt;3-5Y 5.25%, &gt;5Y 5.50%.
 • Corporate (institutional) FD minimum 6 months: 6-9M 2.85%, 1Y 3.25%, &gt;5Y 4.75%.
@@ -1978,27 +7220,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>2083.06.01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67424</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>• Individual '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.
 • Institutional '6 Months to Below 3 Years' 2.75% covers &lt;1Y and 1Y.
@@ -2007,27 +7249,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Green Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>1st Ashoj 2083</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67423</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>• FD bands: 3 Month, 6 Month, 1 Year to below 2 years, 2 to below 4 years, 4 years and above.
 • Institutional 3 Month shown as '-'; 6 Month 2.75% used as &lt;1Y max.</t>
@@ -2035,27 +7277,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67422</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>• Individual: 3M 2.75%, 6M to below 3Y 2.75%, 3-5Y 2.75%, 5Y+ 4.28%.
 • Institutional: 3M '-', all other tenures 2.75%.</t>
@@ -2063,27 +7305,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67421</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>• Individual 3 months to below 2 years 2.75%; '1 year and below 2 years' used as 1 Year.
 • Institutional FD starts at 1 year; &lt;1Y not specified.</t>
@@ -2091,27 +7333,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Ashwin month 2083</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67420</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>• Individual 'Upto 1 Years' 2.80% covers &lt;1Y and 1Y. Locker deposit excluded from saving.
 • Institutional starts 'Above 1 year to 2 year' (2.75%), used as 1 Year; &lt;1Y not specified.</t>
@@ -2119,27 +7361,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Aswin 2083)</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67419</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>• FD starts at 1 year for both individual and institutional; &lt;1Y not specified.
 • In-person individual rates used (mobile app rates are 0.10% higher).
@@ -2149,27 +7391,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>1st Ashoj 2083</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67418</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>• 'All other Savings' 2.75% counted once. FCY and current accounts excluded.
 • Institutional 3M and 6M shown as '-'; &lt;1Y not specified.</t>
@@ -2177,27 +7419,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Narayani Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67417</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>• Individual FD: 3-6M 4.75%, 6-12M 4.95%, 12M above 5.15%.
 • Institutional FD: 3-6M N/A, 6-12M 4.95%, 12M above 5.15% (12M above used as 1 Year).</t>
@@ -2205,54 +7447,54 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Ashoj 01, 2083</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67416</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>• FD bands: 3-9 months, One year, Two year and above.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67415</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 1 Year' 2.75% covers both &lt;1Y and 1Y.
 • Institutional: single rate '6 Months and Above' 2.75% applied to all tenures.</t>
@@ -2260,54 +7502,54 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>2083-06-01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67414</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>• Institutional 2.75% is a single rate for 6 months to below 4 years.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>2083/06/01 (Nepali notice)</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67413</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>• Notice in Nepali. Margin account and current account (0.00%) excluded from saving.
 • Individual '1 year to below 5 years' 3.94% used as 1 Year.
@@ -2316,27 +7558,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Aswin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67446</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>• General FD used; 'Three Months to One Year' 2.77% covers &lt;1Y and 1Y.
 • FCY saving (USD/EUR/GBP) excluded. Special FD products excluded.
@@ -2345,27 +7587,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67445</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>• Institutional FD only listed for '24 Months and above' (2.75%); &lt;1Y and 1Y not specified.
 • Individual 1 Year = '12 Months and below 24 Months' 2.90%.</t>
@@ -2373,27 +7615,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Everest Bank Ltd.</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashoj 2083)</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67385</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>• Individual 'Above 3 years' corrected from 3.50% to 3.75% per EBL correction notice (17 Sep 2026).
 • '3 months upto 3 years' 2.75% covers &lt;1Y and 1Y.</t>
@@ -2401,27 +7643,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Global IME Bank Ltd.</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67443</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 1 Year' 2.76% used for &lt;1Y and 1Y ('Above 1 Year to below 2 Years' is 2.80%).
 • Institutional only 'Above 1 Year' 2.75%, used for 1Y and &gt;1Y; &lt;1Y not specified.</t>
@@ -2429,27 +7671,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67442</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>• This notice only revises USD FD and fixed-rate loans; it states other deposit rates 'remain as it is'.
 • NPR saving/call/FD rates are not in the notice (see HBL's earlier notice or website).</t>
@@ -2457,27 +7699,27 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Kumari Bank Ltd.</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>01 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67441</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>• In-person individual FD rates used; Kumari Smart app rates are higher (2.80% / 3.73%).
 • '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.</t>
@@ -2485,81 +7727,81 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67440</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>• 'Personal' term deposit used as Individual FD.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67439</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>• Individual '6 months to below 3 years' 3.00% covers &lt;1Y and 1Y. Recurring deposit excluded from saving.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Nabil Bank Ltd.</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67438</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>• NPR call rate not published; notice says call deposit rate is as per agreement.
 • Individual '6 months to 1 year' 2.85% used as 1 Year ('Above 1 to 2 years' is 3.00%).</t>
@@ -2567,189 +7809,189 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Nepal Bank Ltd.</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>1st Ashwin 2083</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67437</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>• Individual '3M upto 1Y' 2.76% used for &lt;1Y and 1Y ('Above 1Y upto 2Y' is 3.00%).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67436</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67435</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>NMB Bank Ltd.</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Asoj 1, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67434</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>• Institutional '3 Months to Below 1 Year' shown as '-'.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>01st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67433</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026 (01 Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67432</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>• Individual '6 months to 1 year' 2.75% used as 1 Year ('Above 1 year to 3 years' is 3.10%).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>2083 Asoj 01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67430</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>• Notice in Nepali. General (साधारण) FD used; '1 year to 2 years' 3.15% used as 1 Year.
 • FCY saving excluded.</t>
@@ -2757,108 +7999,108 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Sanima Bank Ltd.</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>Ashwin 1, 2083</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67429</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 12 Months' 2.80% covers &lt;1Y and 1Y; remittance FD excluded.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67428</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67427</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Standard Chartered Bank Nepal Ltd.</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67526</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>• Latest SCB notice (22 Sep 2026) only amends FCY FD rates; NPR rates taken from SCB's 16 Sep notice.
 • Non-individual FD: '1 year and above' 2.75%.</t>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -5061,7 +5061,7 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: EBL.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -8,12 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interest Rate Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Development FD Spread" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly History" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$AB$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly History'!$A$1:$N$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Development FD Spread'!$A$4:$V$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly History'!$A$1:$N$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -114,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +161,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4213,6 +4217,1291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:V19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Development Banks — Fixed Deposit: Individual vs Institutional (Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>3 Months</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>6 Months</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>1 Year (12 Months)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>5 Years &amp; Above</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Institutional</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Corporate Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Garima Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N6" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O6" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q6" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R6" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S6" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T6" s="12" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="U6" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="V6" s="13" t="n">
+        <v>0.0103</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Green Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Jyoti Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="R8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="S8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="12" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="U8" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>0.0153</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Kamana Sewa Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="R9" s="8" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="S9" s="9" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Lumbini Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="N10" s="12" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="O10" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="Q10" s="12" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="R10" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S10" s="13" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="T10" s="12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="U10" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Mahalaxmi Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="S11" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Muktinath Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N12" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O12" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q12" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R12" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S12" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T12" s="12" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="U12" s="12" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>0.0108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Narayani Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="S13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Salapa Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N14" s="12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="O14" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P14" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q14" s="12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="R14" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S14" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T14" s="12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="U14" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V14" s="13" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Shangri-la Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P15" s="9" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="S15" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>0.0153</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Shine Resunga Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N16" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q16" s="12" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="R16" s="12" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="S16" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T16" s="12" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="U16" s="12" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="V16" s="13" t="n">
+        <v>0.0109</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Sindhu Bikash Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>0.0153</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Difference = Individual rate minus Institutional rate (percentage points): green = individuals earn more, red = institutions earn more, grey = same. 'Not specified' = the bank publishes no rate for that tenure (e.g. institutional FD starting at 6 months or 1 year). Rates are the general FD rate applying to a deposit of exactly that tenure; '5 Years &amp; Above' uses the band covering 5 years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:V17"/>
+  <mergeCells count="9">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:D17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(D5),D5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>AND(ISNUMBER(D5),D5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>AND(ISNUMBER(D5),D5=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G17">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>AND(ISNUMBER(G5),G5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>AND(ISNUMBER(G5),G5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>AND(ISNUMBER(G5),G5=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J17">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>AND(ISNUMBER(J5),J5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>AND(ISNUMBER(J5),J5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2">
+      <formula>AND(ISNUMBER(J5),J5=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M5:M17">
+    <cfRule type="expression" priority="10" dxfId="0">
+      <formula>AND(ISNUMBER(M5),M5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="1">
+      <formula>AND(ISNUMBER(M5),M5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="2">
+      <formula>AND(ISNUMBER(M5),M5=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P5:P17">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>AND(ISNUMBER(P5),P5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="1">
+      <formula>AND(ISNUMBER(P5),P5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="2">
+      <formula>AND(ISNUMBER(P5),P5=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S5:S17">
+    <cfRule type="expression" priority="16" dxfId="0">
+      <formula>AND(ISNUMBER(S5),S5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="1">
+      <formula>AND(ISNUMBER(S5),S5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="2">
+      <formula>AND(ISNUMBER(S5),S5=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V5:V17">
+    <cfRule type="expression" priority="19" dxfId="0">
+      <formula>AND(ISNUMBER(V5),V5&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="1">
+      <formula>AND(ISNUMBER(V5),V5&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="21" dxfId="2">
+      <formula>AND(ISNUMBER(V5),V5=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7962,7 +9251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8006,42 +9295,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>All banks</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr"/>
-      <c r="C2" s="18" t="inlineStr"/>
-      <c r="D2" s="18" t="inlineStr"/>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr"/>
+      <c r="C2" s="20" t="inlineStr"/>
+      <c r="D2" s="20" t="inlineStr"/>
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Saving Max is the second highest saving rate, excluding the first highest. Call and FCY accounts are excluded from saving rates; loan, base and spread rates are excluded. Remittance FD rates are excluded from Individual FD. Months follow the Nepali calendar (Shrawan to Ashadh).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Corporate Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67425</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>• Individual FD: 3M 3.50%, 6-9M 3.75%, 1Y 4.25%, &gt;1-2Y 4.50%, &gt;2-3Y 5.00%, &gt;3-5Y 5.25%, &gt;5Y 5.50%.
 • Corporate (institutional) FD minimum 6 months: 6-9M 2.85%, 1Y 3.25%, &gt;5Y 4.75%.
@@ -8050,27 +9339,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>2083.06.01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67424</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>• Individual '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.
 • Institutional '6 Months to Below 3 Years' 2.75% covers &lt;1Y and 1Y.
@@ -8079,27 +9368,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Green Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>1st Ashoj 2083</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67423</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>• FD bands: 3 Month, 6 Month, 1 Year to below 2 years, 2 to below 4 years, 4 years and above.
 • Institutional 3 Month shown as '-'; 6 Month 2.75% used as &lt;1Y max.</t>
@@ -8107,27 +9396,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67422</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>• Individual: 3M 2.75%, 6M to below 3Y 2.75%, 3-5Y 2.75%, 5Y+ 4.28%.
 • Institutional: 3M '-', all other tenures 2.75%.</t>
@@ -8135,27 +9424,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67421</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>• Individual 3 months to below 2 years 2.75%; '1 year and below 2 years' used as 1 Year.
 • Institutional FD starts at 1 year; &lt;1Y not specified.</t>
@@ -8163,27 +9452,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Ashwin month 2083</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67420</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>• Individual 'Upto 1 Years' 2.80% covers &lt;1Y and 1Y. Locker deposit excluded from saving.
 • Institutional starts 'Above 1 year to 2 year' (2.75%), used as 1 Year; &lt;1Y not specified.</t>
@@ -8191,27 +9480,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Aswin 2083)</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67419</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>• FD starts at 1 year for both individual and institutional; &lt;1Y not specified.
 • In-person individual rates used (mobile app rates are 0.10% higher).
@@ -8221,27 +9510,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>1st Ashoj 2083</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67418</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>• 'All other Savings' 2.75% counted once. FCY and current accounts excluded.
 • Institutional 3M and 6M shown as '-'; &lt;1Y not specified.</t>
@@ -8249,27 +9538,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Narayani Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67417</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>• Individual FD: 3-6M 4.75%, 6-12M 4.95%, 12M above 5.15%.
 • Institutional FD: 3-6M N/A, 6-12M 4.95%, 12M above 5.15% (12M above used as 1 Year).</t>
@@ -8277,54 +9566,54 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Ashoj 01, 2083</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67416</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>• FD bands: 3-9 months, One year, Two year and above.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67415</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 1 Year' 2.75% covers both &lt;1Y and 1Y.
 • Institutional: single rate '6 Months and Above' 2.75% applied to all tenures.</t>
@@ -8332,54 +9621,54 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>2083-06-01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67414</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>• Institutional 2.75% is a single rate for 6 months to below 4 years.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>2083/06/01 (Nepali notice)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67413</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>• Notice in Nepali. Margin account and current account (0.00%) excluded from saving.
 • Individual '1 year to below 5 years' 3.94% used as 1 Year.
@@ -8388,27 +9677,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Aswin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67446</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>• General FD used; 'Three Months to One Year' 2.77% covers &lt;1Y and 1Y.
 • FCY saving (USD/EUR/GBP) excluded. Special FD products excluded.
@@ -8417,27 +9706,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67445</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>• Institutional FD only listed for '24 Months and above' (2.75%); &lt;1Y and 1Y not specified.
 • Individual 1 Year = '12 Months and below 24 Months' 2.90%.</t>
@@ -8445,27 +9734,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Everest Bank Ltd.</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashoj 2083)</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67385</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>• Individual 'Above 3 years' corrected from 3.50% to 3.75% per EBL correction notice (17 Sep 2026).
 • '3 months upto 3 years' 2.75% covers &lt;1Y and 1Y.</t>
@@ -8473,27 +9762,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Global IME Bank Ltd.</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67443</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 1 Year' 2.76% used for &lt;1Y and 1Y ('Above 1 Year to below 2 Years' is 2.80%).
 • Institutional only 'Above 1 Year' 2.75%, used for 1Y and &gt;1Y; &lt;1Y not specified.</t>
@@ -8501,27 +9790,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67442</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>• This notice only revises USD FD and fixed-rate loans; it states other deposit rates 'remain as it is'.
 • NPR saving/call/FD rates are not in the notice (see HBL's earlier notice or website).</t>
@@ -8529,27 +9818,27 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Kumari Bank Ltd.</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>01 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67441</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>• In-person individual FD rates used; Kumari Smart app rates are higher (2.80% / 3.73%).
 • '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.</t>
@@ -8557,81 +9846,81 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67440</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>• 'Personal' term deposit used as Individual FD.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67439</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>• Individual '6 months to below 3 years' 3.00% covers &lt;1Y and 1Y. Recurring deposit excluded from saving.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Nabil Bank Ltd.</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67438</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>• NPR call rate not published; notice says call deposit rate is as per agreement.
 • Individual '6 months to 1 year' 2.85% used as 1 Year ('Above 1 to 2 years' is 3.00%).</t>
@@ -8639,189 +9928,189 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Nepal Bank Ltd.</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>1st Ashwin 2083</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67437</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>• Individual '3M upto 1Y' 2.76% used for &lt;1Y and 1Y ('Above 1Y upto 2Y' is 3.00%).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67436</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67435</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>NMB Bank Ltd.</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>Asoj 1, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67434</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>• Institutional '3 Months to Below 1 Year' shown as '-'.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>01st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67433</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026 (01 Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67432</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>• Individual '6 months to 1 year' 2.75% used as 1 Year ('Above 1 year to 3 years' is 3.10%).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>2083 Asoj 01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67430</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>• Notice in Nepali. General (साधारण) FD used; '1 year to 2 years' 3.15% used as 1 Year.
 • FCY saving excluded.</t>
@@ -8829,108 +10118,108 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Sanima Bank Ltd.</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>Ashwin 1, 2083</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67429</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 12 Months' 2.80% covers &lt;1Y and 1Y; remittance FD excluded.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67428</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67427</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Standard Chartered Bank Nepal Ltd.</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67526</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>• Latest SCB notice (22 Sep 2026) only amends FCY FD rates; NPR rates taken from SCB's 16 Sep notice.
 • Non-individual FD: '1 year and above' 2.75%.</t>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -1428,18 +1428,16 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>As per NRB guidelines</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>As per NRB guidelines</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
@@ -2242,18 +2240,16 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Negotiable as per NRB Directive</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>Negotiable as per NRB Directive</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>0.0285</v>
@@ -2440,18 +2436,16 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Up to 50% of minimum saving deposit rate</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>Up to 50% of minimum saving deposit rate</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>0.0276</v>
@@ -2774,18 +2768,16 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Negotiable (max 50% of lowest saving rate)</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Negotiable (max 50% of lowest saving rate)</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="K26" s="8" t="n">
         <v>0.029</v>
@@ -2960,18 +2952,16 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>As per agreement</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>As per agreement</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="K28" s="8" t="n">
         <v>0.0285</v>
@@ -6276,7 +6266,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>As per NRB guidelines</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H14" s="15" t="inlineStr">
@@ -6334,7 +6324,7 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>As per NRB guidelines</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H15" s="16" t="inlineStr">
@@ -7162,7 +7152,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Negotiable as per NRB Directive</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H30" s="8" t="n">
@@ -7220,7 +7210,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>Negotiable as per NRB Directive</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H31" s="12" t="n">
@@ -7386,7 +7376,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Up to 50% of minimum saving deposit rate</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
@@ -7442,7 +7432,7 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>Up to 50% of minimum saving deposit rate</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H35" s="12" t="n">
@@ -7746,7 +7736,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Negotiable (max 50% of lowest saving rate)</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
@@ -7800,7 +7790,7 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>Negotiable (max 50% of lowest saving rate)</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H41" s="12" t="n">
@@ -8180,7 +8170,7 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>As per agreement</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -8234,7 +8224,7 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>As per agreement</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H49" s="12" t="n">
@@ -9305,7 +9295,7 @@
       <c r="D2" s="20" t="inlineStr"/>
       <c r="E2" s="20" t="inlineStr">
         <is>
-          <t>Saving Max is the second highest saving rate, excluding the first highest. Call and FCY accounts are excluded from saving rates; loan, base and spread rates are excluded. Remittance FD rates are excluded from Individual FD. Months follow the Nepali calendar (Shrawan to Ashadh).</t>
+          <t>Saving Max is the second highest saving rate, excluding the first highest. Call and FCY accounts are excluded from saving rates; loan, base and spread rates are excluded. Remittance FD rates are excluded from Individual FD. Where no direct call rate is published (negotiable / as per agreement / 50% of saving rate), Call = 'Up to' 50% of the lowest saving rate. Months follow the Nepali calendar (Shrawan to Ashadh).</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9495,8 @@
           <t>• FD starts at 1 year for both individual and institutional; &lt;1Y not specified.
 • In-person individual rates used (mobile app rates are 0.10% higher).
 • Dollar account, margin locker and PMS accounts excluded from saving.
-• No call rate published; notice says call deposit rate is as per NRB guidelines.</t>
+• No call rate published; notice says call deposit rate is as per NRB guidelines.
+• Call: notice says 'As per NRB guidelines'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9720,8 @@
       <c r="E17" s="20" t="inlineStr">
         <is>
           <t>• Institutional FD only listed for '24 Months and above' (2.75%); &lt;1Y and 1Y not specified.
-• Individual 1 Year = '12 Months and below 24 Months' 2.90%.</t>
+• Individual 1 Year = '12 Months and below 24 Months' 2.90%.
+• Call: notice says 'Negotiable as per NRB Directive'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9777,8 @@
       <c r="E19" s="20" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 1 Year' 2.76% used for &lt;1Y and 1Y ('Above 1 Year to below 2 Years' is 2.80%).
-• Institutional only 'Above 1 Year' 2.75%, used for 1Y and &gt;1Y; &lt;1Y not specified.</t>
+• Institutional only 'Above 1 Year' 2.75%, used for 1Y and &gt;1Y; &lt;1Y not specified.
+• Call: notice says 'Up to 50% of minimum saving deposit rate'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9861,8 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>• 'Personal' term deposit used as Individual FD.</t>
+          <t>• 'Personal' term deposit used as Individual FD.
+• Call: notice says 'Negotiable (max 50% of lowest saving rate)'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9917,8 @@
       <c r="E24" s="20" t="inlineStr">
         <is>
           <t>• NPR call rate not published; notice says call deposit rate is as per agreement.
-• Individual '6 months to 1 year' 2.85% used as 1 Year ('Above 1 to 2 years' is 3.00%).</t>
+• Individual '6 months to 1 year' 2.85% used as 1 Year ('Above 1 to 2 years' is 3.00%).
+• Call: notice says 'As per agreement'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -36,7 +36,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000B2447"/>
+      <color rgb="000B4EA2"/>
       <sz val="14"/>
     </font>
     <font>
@@ -45,7 +45,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000B2447"/>
+      <color rgb="000B4EA2"/>
     </font>
     <font>
       <i val="1"/>
@@ -57,7 +57,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,27 +66,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B2447"/>
+        <fgColor rgb="000B4EA2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0019376D"/>
+        <fgColor rgb="002F6BBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0024477F"/>
+        <fgColor rgb="006FA52E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E7F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F9FD"/>
+        <fgColor rgb="00EEF5E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,23 +95,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="008EA9C1"/>
+        <color rgb="00C9D3E0"/>
       </left>
       <right style="thin">
-        <color rgb="008EA9C1"/>
+        <color rgb="00C9D3E0"/>
       </right>
       <top style="thin">
-        <color rgb="008EA9C1"/>
+        <color rgb="00C9D3E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="008EA9C1"/>
+        <color rgb="00C9D3E0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -142,27 +137,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -174,33 +153,31 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="00006100"/>
+        <color rgb="003F6F12"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
+          <fgColor rgb="00E3F1D3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="009C0006"/>
+        <color rgb="00B42318"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
+          <fgColor rgb="00FBE3E1"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="00595959"/>
+        <color rgb="006B7280"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00EDEDED"/>
-        </patternFill>
+        <patternFill/>
       </fill>
     </dxf>
     <dxf>
@@ -804,7 +781,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Development Banks</t>
@@ -838,7 +815,7 @@
       <c r="AA5" s="6" t="n"/>
       <c r="AB5" s="6" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Corporate Development Bank Ltd.</t>
@@ -930,99 +907,99 @@
         <v>-0.0025</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n">
+      <c r="B7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="G7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="G7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="J7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="12" t="n">
+      <c r="J7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="R7" s="12" t="n">
+      <c r="R7" s="8" t="n">
         <v>0.0441</v>
       </c>
-      <c r="S7" s="13" t="n">
+      <c r="S7" s="9" t="n">
         <v>-0.0013</v>
       </c>
-      <c r="T7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="12" t="n">
+      <c r="T7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="AA7" s="12" t="n">
+      <c r="AA7" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="AB7" s="13" t="n">
+      <c r="AB7" s="9" t="n">
         <v>-0.0025</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Green Development Bank Ltd.</t>
@@ -1114,99 +1091,99 @@
         <v>-0.003</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="B9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="J9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="12" t="n">
+      <c r="J9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="8" t="n">
         <v>0.0441</v>
       </c>
-      <c r="S9" s="13" t="n">
+      <c r="S9" s="9" t="n">
         <v>-0.0013</v>
       </c>
-      <c r="T9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AB9" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="T9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AB9" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Kamana Sewa Bikas Bank Ltd.</t>
@@ -1270,17 +1247,17 @@
       <c r="S10" s="9" t="n">
         <v>-0.0013</v>
       </c>
-      <c r="T10" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U10" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V10" s="15" t="inlineStr">
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U10" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1304,105 +1281,105 @@
         <v>-0.0015</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="n">
+      <c r="B11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="9" t="n">
         <v>-0.001</v>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="J11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="12" t="n">
+      <c r="J11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="L11" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="M11" s="13" t="n">
+      <c r="M11" s="9" t="n">
         <v>-0.001</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="O11" s="12" t="n">
+      <c r="O11" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="P11" s="13" t="n">
+      <c r="P11" s="9" t="n">
         <v>-0.001</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="R11" s="12" t="n">
+      <c r="R11" s="8" t="n">
         <v>0.046</v>
       </c>
-      <c r="S11" s="13" t="n">
+      <c r="S11" s="9" t="n">
         <v>-0.001</v>
       </c>
-      <c r="T11" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U11" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V11" s="16" t="inlineStr">
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W11" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X11" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="12" t="n">
+      <c r="W11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="AA11" s="12" t="n">
+      <c r="AA11" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB11" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="AB11" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Mahalaxmi Bikas Bank Ltd.</t>
@@ -1439,17 +1416,17 @@
       <c r="J12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M12" s="15" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1472,17 +1449,17 @@
       <c r="S12" s="9" t="n">
         <v>-0.002</v>
       </c>
-      <c r="T12" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U12" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V12" s="15" t="inlineStr">
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U12" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1506,103 +1483,103 @@
         <v>-0.002</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12" t="n">
+      <c r="B13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="G13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Up to 1.00%</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Up to 1.00%</t>
         </is>
       </c>
-      <c r="J13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="12" t="n">
+      <c r="J13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="R13" s="12" t="n">
+      <c r="R13" s="8" t="n">
         <v>0.0441</v>
       </c>
-      <c r="S13" s="13" t="n">
+      <c r="S13" s="9" t="n">
         <v>-0.0013</v>
       </c>
-      <c r="T13" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V13" s="16" t="inlineStr">
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V13" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="12" t="n">
+      <c r="W13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="8" t="n">
         <v>0.032</v>
       </c>
-      <c r="AA13" s="12" t="n">
+      <c r="AA13" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="AB13" s="13" t="n">
+      <c r="AB13" s="9" t="n">
         <v>-0.0005</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Narayani Development Bank Ltd.</t>
@@ -1694,99 +1671,99 @@
         <v>-0.0025</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="12" t="n">
+      <c r="B15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="G15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="J15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="12" t="n">
+      <c r="J15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="L15" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="M15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="12" t="n">
+      <c r="M15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="O15" s="12" t="n">
+      <c r="O15" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="P15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="12" t="n">
+      <c r="P15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="R15" s="12" t="n">
+      <c r="R15" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="S15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="12" t="n">
+      <c r="S15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="U15" s="12" t="n">
+      <c r="U15" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="V15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="12" t="n">
+      <c r="V15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="X15" s="12" t="n">
+      <c r="X15" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="Y15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="12" t="n">
+      <c r="Y15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AA15" s="12" t="n">
+      <c r="AA15" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AB15" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="AB15" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Shangri-la Development Bank Ltd.</t>
@@ -1878,99 +1855,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="B17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="G17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="J17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="12" t="n">
+      <c r="J17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="O17" s="12" t="n">
+      <c r="O17" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="P17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="12" t="n">
+      <c r="P17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>0.0459</v>
       </c>
-      <c r="R17" s="12" t="n">
+      <c r="R17" s="8" t="n">
         <v>0.0459</v>
       </c>
-      <c r="S17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="12" t="n">
+      <c r="S17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="AA17" s="12" t="n">
+      <c r="AA17" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="AB17" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="AB17" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Sindhu Bikash Bank Ltd.</t>
@@ -1979,12 +1956,12 @@
       <c r="B18" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1992,12 +1969,12 @@
       <c r="E18" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2007,12 +1984,12 @@
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2020,12 +1997,12 @@
       <c r="K18" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="L18" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M18" s="15" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2051,12 +2028,12 @@
       <c r="T18" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="U18" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V18" s="15" t="inlineStr">
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2064,12 +2041,12 @@
       <c r="W18" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="X18" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="Y18" s="15" t="inlineStr">
+      <c r="X18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="Y18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2077,18 +2054,18 @@
       <c r="Z18" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="AA18" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="AB18" s="15" t="inlineStr">
+      <c r="AA18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="AB18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
@@ -2122,7 +2099,7 @@
       <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Agricultural Development Bank Ltd.</t>
@@ -2214,111 +2191,111 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="12" t="n">
+      <c r="B21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="G21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="J21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="12" t="n">
+      <c r="J21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="M21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="12" t="n">
+      <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="O21" s="12" t="n">
+      <c r="O21" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="P21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="12" t="n">
+      <c r="P21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="R21" s="12" t="n">
+      <c r="R21" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="S21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U21" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V21" s="16" t="inlineStr">
+      <c r="S21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W21" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="X21" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="Y21" s="16" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="X21" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="Y21" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z21" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA21" s="12" t="n">
+      <c r="Z21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA21" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB21" s="13" t="n">
+      <c r="AB21" s="9" t="n">
         <v>-0.0025</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Everest Bank Ltd.</t>
@@ -2410,339 +2387,339 @@
         <v>-0.0025</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Global IME Bank Ltd.</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="B23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="J23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="12" t="n">
+      <c r="J23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="L23" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="M23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="12" t="n">
+      <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="O23" s="12" t="n">
+      <c r="O23" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="P23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="12" t="n">
+      <c r="P23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="R23" s="12" t="n">
+      <c r="R23" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="S23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U23" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V23" s="16" t="inlineStr">
+      <c r="S23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U23" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AB23" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="W23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AB23" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M24" s="15" t="inlineStr">
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="O24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="P24" s="15" t="inlineStr">
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="S24" s="15" t="inlineStr">
+      <c r="Q24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="R24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V24" s="15" t="inlineStr">
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="X24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="Y24" s="15" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="X24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="Y24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="AA24" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="AB24" s="15" t="inlineStr">
+      <c r="Z24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="AA24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="AB24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Kumari Bank Ltd.</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="12" t="n">
+      <c r="B25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8" t="n">
         <v>0.0391</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="8" t="n">
         <v>0.0391</v>
       </c>
-      <c r="G25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="G25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Up to 0.81%</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Up to 0.81%</t>
         </is>
       </c>
-      <c r="J25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="12" t="n">
+      <c r="J25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>0.0343</v>
       </c>
-      <c r="R25" s="12" t="n">
+      <c r="R25" s="8" t="n">
         <v>0.0346</v>
       </c>
-      <c r="S25" s="13" t="n">
+      <c r="S25" s="9" t="n">
         <v>-0.0003</v>
       </c>
-      <c r="T25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="12" t="n">
+      <c r="T25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="AA25" s="12" t="n">
+      <c r="AA25" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="AB25" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="AB25" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Laxmi Sunrise Bank Ltd.</t>
@@ -2834,99 +2811,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C27" s="12" t="n">
+      <c r="B27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C27" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="9" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="9" t="n">
         <v>-0.0021</v>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Up to 0.25%</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Up to 0.25%</t>
         </is>
       </c>
-      <c r="J27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="12" t="n">
+      <c r="J27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="L27" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="M27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="12" t="n">
+      <c r="M27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="O27" s="12" t="n">
+      <c r="O27" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="P27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="12" t="n">
+      <c r="P27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="R27" s="12" t="n">
+      <c r="R27" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="S27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="12" t="n">
+      <c r="S27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="AA27" s="12" t="n">
+      <c r="AA27" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB27" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="AB27" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Nabil Bank Ltd.</t>
@@ -3018,99 +2995,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Nepal Bank Ltd.</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="C29" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D29" s="13" t="n">
+      <c r="C29" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D29" s="9" t="n">
         <v>0.0001</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="9" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>0.20%</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>0.40%</t>
         </is>
       </c>
-      <c r="J29" s="13" t="n">
+      <c r="J29" s="9" t="n">
         <v>-0.002</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="K29" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="L29" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="M29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="12" t="n">
+      <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="O29" s="12" t="n">
+      <c r="O29" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="P29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="12" t="n">
+      <c r="P29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="8" t="n">
         <v>0.0415</v>
       </c>
-      <c r="R29" s="12" t="n">
+      <c r="R29" s="8" t="n">
         <v>0.0415</v>
       </c>
-      <c r="S29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U29" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X29" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="12" t="n">
+      <c r="S29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="AA29" s="12" t="n">
+      <c r="AA29" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="AB29" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="AB29" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>NIC Asia Bank Ltd.</t>
@@ -3202,105 +3179,105 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C31" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="12" t="n">
+      <c r="B31" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="G31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="G31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>Up to 1.35%</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Up to 1.35%</t>
         </is>
       </c>
-      <c r="J31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="12" t="n">
+      <c r="J31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="L31" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="M31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="12" t="n">
+      <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="O31" s="12" t="n">
+      <c r="O31" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="P31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="12" t="n">
+      <c r="P31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="R31" s="12" t="n">
+      <c r="R31" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="S31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U31" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V31" s="16" t="inlineStr">
+      <c r="S31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W31" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X31" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="12" t="n">
+      <c r="W31" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="AA31" s="12" t="n">
+      <c r="AA31" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="AB31" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="AB31" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t>NMB Bank Ltd.</t>
@@ -3364,7 +3341,7 @@
       <c r="S32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="15" t="inlineStr">
+      <c r="T32" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -3372,7 +3349,7 @@
       <c r="U32" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="V32" s="15" t="inlineStr">
+      <c r="V32" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3396,99 +3373,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C33" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="D33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12" t="n">
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>0.0302</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="8" t="n">
         <v>0.0302</v>
       </c>
-      <c r="G33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="G33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="J33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="12" t="n">
+      <c r="J33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="M33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="12" t="n">
+      <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="O33" s="12" t="n">
+      <c r="O33" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="P33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="12" t="n">
+      <c r="P33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="R33" s="12" t="n">
+      <c r="R33" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="S33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AB33" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="S33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AB33" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Prabhu Bank Ltd.</t>
@@ -3580,99 +3557,99 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="12" t="n">
+      <c r="B35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="G35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="J35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="12" t="n">
+      <c r="J35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="L35" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="M35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="12" t="n">
+      <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8" t="n">
         <v>0.0315</v>
       </c>
-      <c r="O35" s="12" t="n">
+      <c r="O35" s="8" t="n">
         <v>0.0315</v>
       </c>
-      <c r="P35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="12" t="n">
+      <c r="P35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="R35" s="12" t="n">
+      <c r="R35" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="S35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="12" t="n">
+      <c r="S35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="AA35" s="12" t="n">
+      <c r="AA35" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="AB35" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="AB35" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Sanima Bank Ltd.</t>
@@ -3764,99 +3741,99 @@
         <v>0.0021</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C37" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="12" t="n">
+      <c r="B37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="8" t="n">
         <v>0.0279</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F37" s="8" t="n">
         <v>0.0279</v>
       </c>
-      <c r="G37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="G37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Up to 0.75%</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Up to 0.75%</t>
         </is>
       </c>
-      <c r="J37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="12" t="n">
+      <c r="J37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="L37" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="M37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="12" t="n">
+      <c r="M37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="8" t="n">
         <v>0.032</v>
       </c>
-      <c r="O37" s="12" t="n">
+      <c r="O37" s="8" t="n">
         <v>0.032</v>
       </c>
-      <c r="P37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="12" t="n">
+      <c r="P37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>0.04099999999999999</v>
       </c>
-      <c r="R37" s="12" t="n">
+      <c r="R37" s="8" t="n">
         <v>0.04099999999999999</v>
       </c>
-      <c r="S37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U37" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X37" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA37" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AB37" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="S37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AB37" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Siddhartha Bank Ltd.</t>
@@ -3920,17 +3897,17 @@
       <c r="S38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U38" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V38" s="15" t="inlineStr">
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U38" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V38" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3954,106 +3931,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Standard Chartered Bank Nepal Ltd.</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="B39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>Up to 0.20%</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Up to 0.25%</t>
         </is>
       </c>
-      <c r="J39" s="13" t="n">
+      <c r="J39" s="9" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="K39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="12" t="n">
+      <c r="K39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="R39" s="12" t="n">
+      <c r="R39" s="8" t="n">
         <v>0.038</v>
       </c>
-      <c r="S39" s="13" t="n">
+      <c r="S39" s="9" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="T39" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U39" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V39" s="16" t="inlineStr">
+      <c r="T39" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U39" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V39" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AB39" s="13" t="n">
+      <c r="W39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AB39" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
         </is>
@@ -4405,8 +4382,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Corporate Development Bank Ltd.</t>
         </is>
@@ -4414,12 +4391,12 @@
       <c r="B5" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4479,82 +4456,82 @@
         <v>0.0075</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="B6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I6" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="12" t="n">
+      <c r="E6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="L6" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M6" s="13" t="n">
+      <c r="L6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M6" s="9" t="n">
         <v>0.0025</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="O6" s="12" t="n">
+      <c r="O6" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="P6" s="13" t="n">
+      <c r="P6" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="S6" s="13" t="n">
+      <c r="S6" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="T6" s="12" t="n">
+      <c r="T6" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="U6" s="12" t="n">
+      <c r="U6" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="V6" s="13" t="n">
+      <c r="V6" s="9" t="n">
         <v>0.0103</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Green Development Bank Ltd.</t>
         </is>
@@ -4562,12 +4539,12 @@
       <c r="B7" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4627,82 +4604,82 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="B8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="R8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="S8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="12" t="n">
+      <c r="E8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="U8" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V8" s="13" t="n">
+      <c r="U8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V8" s="9" t="n">
         <v>0.0153</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
@@ -4710,12 +4687,12 @@
       <c r="B9" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4723,12 +4700,12 @@
       <c r="E9" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4779,116 +4756,116 @@
         <v>0.009299999999999999</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J10" s="13" t="n">
+      <c r="I10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J10" s="9" t="n">
         <v>0.0005</v>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="L10" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M10" s="13" t="n">
+      <c r="L10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M10" s="9" t="n">
         <v>0.0015</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="O10" s="12" t="n">
+      <c r="O10" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="9" t="n">
         <v>-0.001</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="8" t="n">
         <v>0.034</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="S10" s="13" t="n">
+      <c r="S10" s="9" t="n">
         <v>0.004</v>
       </c>
-      <c r="T10" s="12" t="n">
+      <c r="T10" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="U10" s="12" t="n">
+      <c r="U10" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="V10" s="13" t="n">
+      <c r="V10" s="9" t="n">
         <v>0.015</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4939,86 +4916,86 @@
         <v>0.0005</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="B12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="E12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12" t="n">
+      <c r="H12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="M12" s="13" t="n">
+      <c r="M12" s="9" t="n">
         <v>0.002</v>
       </c>
-      <c r="N12" s="12" t="n">
+      <c r="N12" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="O12" s="12" t="n">
+      <c r="O12" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="Q12" s="12" t="n">
+      <c r="Q12" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="R12" s="12" t="n">
+      <c r="R12" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="S12" s="13" t="n">
+      <c r="S12" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="T12" s="12" t="n">
+      <c r="T12" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="U12" s="12" t="n">
+      <c r="U12" s="8" t="n">
         <v>0.032</v>
       </c>
-      <c r="V12" s="13" t="n">
+      <c r="V12" s="9" t="n">
         <v>0.0108</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Narayani Development Bank Ltd.</t>
         </is>
@@ -5026,12 +5003,12 @@
       <c r="B13" s="8" t="n">
         <v>0.0475</v>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5091,78 +5068,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="9" t="n">
         <v>0.0075</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="K14" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L14" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="M14" s="13" t="n">
+      <c r="M14" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="N14" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="O14" s="12" t="n">
+      <c r="O14" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="P14" s="13" t="n">
+      <c r="P14" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="Q14" s="12" t="n">
+      <c r="Q14" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="R14" s="12" t="n">
+      <c r="R14" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="S14" s="13" t="n">
+      <c r="S14" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="T14" s="12" t="n">
+      <c r="T14" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="U14" s="12" t="n">
+      <c r="U14" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="V14" s="13" t="n">
+      <c r="V14" s="9" t="n">
         <v>0.005</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Shangri-la Development Bank Ltd.</t>
         </is>
@@ -5170,12 +5147,12 @@
       <c r="B15" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5235,84 +5212,84 @@
         <v>0.0153</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12" t="n">
+      <c r="E16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J16" s="13" t="n">
+      <c r="I16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J16" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="L16" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M16" s="13" t="n">
+      <c r="L16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M16" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="N16" s="12" t="n">
+      <c r="N16" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="O16" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P16" s="13" t="n">
+      <c r="O16" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P16" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="Q16" s="12" t="n">
+      <c r="Q16" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="R16" s="12" t="n">
+      <c r="R16" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="S16" s="13" t="n">
+      <c r="S16" s="9" t="n">
         <v>0.005</v>
       </c>
-      <c r="T16" s="12" t="n">
+      <c r="T16" s="8" t="n">
         <v>0.0459</v>
       </c>
-      <c r="U16" s="12" t="n">
+      <c r="U16" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="V16" s="13" t="n">
+      <c r="V16" s="9" t="n">
         <v>0.0109</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Sindhu Bikash Bank Ltd.</t>
         </is>
@@ -5320,12 +5297,12 @@
       <c r="B17" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5386,7 +5363,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Difference = Individual rate minus Institutional rate (percentage points): green = individuals earn more, red = institutions earn more, grey = same. 'Not specified' = the bank publishes no rate for that tenure (e.g. institutional FD starting at 6 months or 1 year). Rates are the general FD rate applying to a deposit of exactly that tenure; '5 Years &amp; Above' uses the band covering 5 years.</t>
         </is>
@@ -5638,54 +5615,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Corporate Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Up to 1.42%</t>
         </is>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H3" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="J3" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="K3" s="12" t="n">
+      <c r="K3" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="L3" s="12" t="n">
+      <c r="L3" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="M3" s="12" t="n">
+      <c r="M3" s="8" t="n">
         <v>0.0475</v>
       </c>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
@@ -5746,54 +5723,54 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F5" s="12" t="n">
+      <c r="E5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="H5" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J5" s="12" t="n">
+      <c r="H5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J5" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="K5" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M5" s="12" t="n">
+      <c r="K5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M5" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>2083.06.01 (17 Sep 2026)</t>
         </is>
@@ -5854,54 +5831,54 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Green Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="E7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="8" t="n">
         <v>0.0525</v>
       </c>
-      <c r="K7" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L7" s="12" t="n">
+      <c r="K7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>1st Ashoj 2083</t>
         </is>
@@ -5962,54 +5939,54 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="E9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J9" s="12" t="n">
+      <c r="H9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J9" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="K9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="K9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
@@ -6054,7 +6031,7 @@
       <c r="J10" s="8" t="n">
         <v>0.0441</v>
       </c>
-      <c r="K10" s="15" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -6072,56 +6049,56 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F11" s="12" t="n">
+      <c r="E11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H11" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J11" s="12" t="n">
+      <c r="H11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J11" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M11" s="12" t="n">
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>0.0335</v>
       </c>
-      <c r="N11" s="14" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
@@ -6166,7 +6143,7 @@
       <c r="J12" s="8" t="n">
         <v>0.046</v>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -6184,56 +6161,56 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F13" s="12" t="n">
+      <c r="E13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M13" s="12" t="n">
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>Ashwin month 2083</t>
         </is>
@@ -6269,7 +6246,7 @@
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -6280,7 +6257,7 @@
       <c r="J14" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -6298,58 +6275,58 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="E15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="n">
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="8" t="n">
         <v>0.043</v>
       </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M15" s="12" t="n">
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M15" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="N15" s="14" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Aswin 2083)</t>
         </is>
@@ -6410,56 +6387,56 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F17" s="12" t="n">
+      <c r="E17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F17" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Up to 1.00%</t>
         </is>
       </c>
-      <c r="H17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J17" s="12" t="n">
+      <c r="H17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J17" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M17" s="12" t="n">
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>0.032</v>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>1st Ashoj 2083</t>
         </is>
@@ -6520,54 +6497,54 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Narayani Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="E19" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>1.375%</t>
         </is>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="H19" s="8" t="n">
         <v>0.0495</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="8" t="n">
         <v>0.0515</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="J19" s="8" t="n">
         <v>0.0515</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="K19" s="8" t="n">
         <v>0.0495</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="8" t="n">
         <v>0.0515</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="8" t="n">
         <v>0.0515</v>
       </c>
-      <c r="N19" s="14" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
@@ -6628,54 +6605,54 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F21" s="12" t="n">
+      <c r="E21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="H21" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="8" t="n">
         <v>0.055</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="K21" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="M21" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="N21" s="14" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>Ashoj 01, 2083</t>
         </is>
@@ -6736,54 +6713,54 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="E23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J23" s="12" t="n">
+      <c r="H23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J23" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="K23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
+      <c r="K23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
@@ -6844,54 +6821,54 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F25" s="12" t="n">
+      <c r="E25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I25" s="12" t="n">
+      <c r="H25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I25" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="J25" s="8" t="n">
         <v>0.0459</v>
       </c>
-      <c r="K25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M25" s="12" t="n">
+      <c r="K25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M25" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="N25" s="14" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>2083-06-01 (17 Sep 2026)</t>
         </is>
@@ -6916,22 +6893,22 @@
       <c r="D26" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -6942,17 +6919,17 @@
       <c r="J26" s="8" t="n">
         <v>0.0441</v>
       </c>
-      <c r="K26" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M26" s="15" t="inlineStr">
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -6964,54 +6941,54 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F27" s="12" t="n">
+      <c r="E27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I27" s="12" t="n">
+      <c r="H27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I27" s="8" t="n">
         <v>0.0394</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="J27" s="8" t="n">
         <v>0.0428</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N27" s="14" t="inlineStr">
+      <c r="K27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>2083/06/01 (Nepali notice)</t>
         </is>
@@ -7072,54 +7049,54 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="8" t="n">
         <v>0.0304</v>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>0.45%</t>
         </is>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="H29" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="I29" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="J29" s="8" t="n">
         <v>0.0415</v>
       </c>
-      <c r="K29" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N29" s="14" t="inlineStr">
+      <c r="K29" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>Aswin 01, 2083 (17 Sep 2026)</t>
         </is>
@@ -7164,12 +7141,12 @@
       <c r="J30" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L30" s="15" t="inlineStr">
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -7184,58 +7161,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F31" s="12" t="n">
+      <c r="E31" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F31" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="H31" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="I31" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="J31" s="8" t="n">
         <v>0.0385</v>
       </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L31" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N31" s="14" t="inlineStr">
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
@@ -7296,54 +7273,54 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Everest Bank Ltd.</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="E33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Up to 0.50%</t>
         </is>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J33" s="12" t="n">
+      <c r="H33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J33" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M33" s="12" t="n">
+      <c r="K33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M33" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="N33" s="14" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashoj 2083)</t>
         </is>
@@ -7388,7 +7365,7 @@
       <c r="J34" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -7406,56 +7383,56 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Global IME Bank Ltd.</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D35" s="14" t="n">
+      <c r="D35" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="E35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="H35" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="I35" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="J35" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="K35" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N35" s="14" t="inlineStr">
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
@@ -7480,47 +7457,47 @@
       <c r="D36" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J36" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K36" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L36" s="15" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M36" s="15" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -7532,70 +7509,70 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D37" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M37" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
@@ -7656,54 +7633,54 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Kumari Bank Ltd.</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D39" s="14" t="n">
+      <c r="D39" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F39" s="12" t="n">
+      <c r="E39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F39" s="8" t="n">
         <v>0.0391</v>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>Up to 0.81%</t>
         </is>
       </c>
-      <c r="H39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J39" s="12" t="n">
+      <c r="H39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J39" s="8" t="n">
         <v>0.0343</v>
       </c>
-      <c r="K39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M39" s="12" t="n">
+      <c r="K39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M39" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="N39" s="14" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>01 Ashwin 2083 (17 Sep 2026)</t>
         </is>
@@ -7764,54 +7741,54 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E41" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F41" s="12" t="n">
+      <c r="E41" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="H41" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="I41" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="J41" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="K41" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M41" s="12" t="n">
+      <c r="K41" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M41" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="N41" s="14" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
@@ -7872,54 +7849,54 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D43" s="14" t="n">
+      <c r="D43" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E43" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F43" s="12" t="n">
+      <c r="E43" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F43" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>Up to 0.25%</t>
         </is>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="H43" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="I43" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="J43" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="K43" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M43" s="12" t="n">
+      <c r="K43" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M43" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="N43" s="14" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
@@ -7980,54 +7957,54 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D45" s="14" t="n">
+      <c r="D45" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E45" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="E45" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J45" s="12" t="n">
+      <c r="H45" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J45" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="K45" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M45" s="12" t="n">
+      <c r="K45" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M45" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="N45" s="14" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
@@ -8088,56 +8065,56 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>NMB Bank Ltd.</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D47" s="14" t="n">
+      <c r="D47" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E47" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="E47" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H47" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I47" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J47" s="12" t="n">
+      <c r="H47" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J47" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M47" s="12" t="n">
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M47" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="N47" s="14" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>Asoj 1, 2083 (17 Sep 2026)</t>
         </is>
@@ -8198,54 +8175,54 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>Nabil Bank Ltd.</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D49" s="14" t="n">
+      <c r="D49" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E49" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F49" s="12" t="n">
+      <c r="E49" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F49" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G49" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="H49" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="I49" s="8" t="n">
         <v>0.0285</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="J49" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="K49" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M49" s="12" t="n">
+      <c r="K49" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M49" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="N49" s="14" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashwin 2083)</t>
         </is>
@@ -8306,54 +8283,54 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Nepal Bank Ltd.</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="F51" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>0.20%</t>
         </is>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="H51" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="I51" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="J51" s="8" t="n">
         <v>0.0415</v>
       </c>
-      <c r="K51" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M51" s="12" t="n">
+      <c r="K51" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M51" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="N51" s="14" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>1st Ashwin 2083</t>
         </is>
@@ -8398,7 +8375,7 @@
       <c r="J52" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="K52" s="15" t="inlineStr">
+      <c r="K52" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -8416,56 +8393,56 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D53" s="14" t="n">
+      <c r="D53" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E53" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F53" s="12" t="n">
+      <c r="E53" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F53" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>Up to 1.35%</t>
         </is>
       </c>
-      <c r="H53" s="12" t="n">
+      <c r="H53" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="I53" s="12" t="n">
+      <c r="I53" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="J53" s="12" t="n">
+      <c r="J53" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M53" s="12" t="n">
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M53" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="N53" s="14" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
@@ -8526,54 +8503,54 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D55" s="14" t="n">
+      <c r="D55" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E55" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F55" s="12" t="n">
+      <c r="E55" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F55" s="8" t="n">
         <v>0.0279</v>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>Up to 0.75%</t>
         </is>
       </c>
-      <c r="H55" s="12" t="n">
+      <c r="H55" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="I55" s="12" t="n">
+      <c r="I55" s="8" t="n">
         <v>0.032</v>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="J55" s="8" t="n">
         <v>0.04099999999999999</v>
       </c>
-      <c r="K55" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N55" s="14" t="inlineStr">
+      <c r="K55" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M55" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
@@ -8634,54 +8611,54 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C57" s="14" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D57" s="14" t="n">
+      <c r="D57" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E57" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F57" s="12" t="n">
+      <c r="E57" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F57" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G57" s="14" t="inlineStr">
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>Up to 0.10%</t>
         </is>
       </c>
-      <c r="H57" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I57" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J57" s="12" t="n">
+      <c r="H57" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J57" s="8" t="n">
         <v>0.0455</v>
       </c>
-      <c r="K57" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N57" s="14" t="inlineStr">
+      <c r="K57" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026 (01 Ashwin 2083)</t>
         </is>
@@ -8742,54 +8719,54 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C59" s="14" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D59" s="14" t="n">
+      <c r="D59" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="E59" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="F59" s="12" t="n">
+      <c r="F59" s="8" t="n">
         <v>0.0302</v>
       </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="H59" s="12" t="n">
+      <c r="H59" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="I59" s="12" t="n">
+      <c r="I59" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="J59" s="12" t="n">
+      <c r="J59" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="K59" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N59" s="14" t="inlineStr">
+      <c r="K59" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M59" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>01st Ashwin 2083 (17 Sep 2026)</t>
         </is>
@@ -8850,54 +8827,54 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C61" s="14" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D61" s="14" t="n">
+      <c r="D61" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E61" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F61" s="12" t="n">
+      <c r="E61" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F61" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G61" s="14" t="inlineStr">
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="H61" s="12" t="n">
+      <c r="H61" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="I61" s="12" t="n">
+      <c r="I61" s="8" t="n">
         <v>0.0315</v>
       </c>
-      <c r="J61" s="12" t="n">
+      <c r="J61" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="K61" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M61" s="12" t="n">
+      <c r="K61" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M61" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="N61" s="14" t="inlineStr">
+      <c r="N61" s="10" t="inlineStr">
         <is>
           <t>2083 Asoj 01 (17 Sep 2026)</t>
         </is>
@@ -8958,54 +8935,54 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>Sanima Bank Ltd.</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C63" s="14" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D63" s="14" t="n">
+      <c r="D63" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E63" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F63" s="12" t="n">
+      <c r="E63" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F63" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="G63" s="14" t="inlineStr">
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="H63" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="I63" s="12" t="n">
+      <c r="I63" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="J63" s="12" t="n">
+      <c r="J63" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="K63" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L63" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M63" s="12" t="n">
+      <c r="K63" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L63" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M63" s="8" t="n">
         <v>0.0351</v>
       </c>
-      <c r="N63" s="14" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>Ashwin 1, 2083</t>
         </is>
@@ -9050,7 +9027,7 @@
       <c r="J64" s="8" t="n">
         <v>0.03759999999999999</v>
       </c>
-      <c r="K64" s="15" t="inlineStr">
+      <c r="K64" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -9068,56 +9045,56 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C65" s="14" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D65" s="14" t="n">
+      <c r="D65" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E65" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F65" s="12" t="n">
+      <c r="E65" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F65" s="8" t="n">
         <v>0.0305</v>
       </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>Up to 0.25%</t>
         </is>
       </c>
-      <c r="H65" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I65" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J65" s="12" t="n">
+      <c r="H65" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I65" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J65" s="8" t="n">
         <v>0.03759999999999999</v>
       </c>
-      <c r="K65" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M65" s="12" t="n">
+      <c r="K65" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L65" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M65" s="8" t="n">
         <v>0.0305</v>
       </c>
-      <c r="N65" s="14" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
@@ -9162,7 +9139,7 @@
       <c r="J66" s="8" t="n">
         <v>0.038</v>
       </c>
-      <c r="K66" s="15" t="inlineStr">
+      <c r="K66" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -9180,56 +9157,56 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>Standard Chartered Bank Nepal Ltd.</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C67" s="14" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="D67" s="14" t="n">
+      <c r="D67" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E67" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F67" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="E67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>Up to 0.20%</t>
         </is>
       </c>
-      <c r="H67" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J67" s="12" t="n">
+      <c r="H67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J67" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="K67" s="16" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N67" s="14" t="inlineStr">
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
@@ -9285,42 +9262,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>All banks</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr"/>
-      <c r="C2" s="20" t="inlineStr"/>
-      <c r="D2" s="20" t="inlineStr"/>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr"/>
+      <c r="C2" s="14" t="inlineStr"/>
+      <c r="D2" s="14" t="inlineStr"/>
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>Saving Max is the second highest saving rate, excluding the first highest. Call and FCY accounts are excluded from saving rates; loan, base and spread rates are excluded. Remittance FD rates are excluded from Individual FD. Where no direct call rate is published (negotiable / as per agreement / 50% of saving rate), Call = 'Up to' 50% of the lowest saving rate. Months follow the Nepali calendar (Shrawan to Ashadh).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Corporate Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67425</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>• Individual FD: 3M 3.50%, 6-9M 3.75%, 1Y 4.25%, &gt;1-2Y 4.50%, &gt;2-3Y 5.00%, &gt;3-5Y 5.25%, &gt;5Y 5.50%.
 • Corporate (institutional) FD minimum 6 months: 6-9M 2.85%, 1Y 3.25%, &gt;5Y 4.75%.
@@ -9329,27 +9306,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>2083.06.01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67424</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>• Individual '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.
 • Institutional '6 Months to Below 3 Years' 2.75% covers &lt;1Y and 1Y.
@@ -9358,27 +9335,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Green Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>1st Ashoj 2083</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67423</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>• FD bands: 3 Month, 6 Month, 1 Year to below 2 years, 2 to below 4 years, 4 years and above.
 • Institutional 3 Month shown as '-'; 6 Month 2.75% used as &lt;1Y max.</t>
@@ -9386,27 +9363,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67422</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>• Individual: 3M 2.75%, 6M to below 3Y 2.75%, 3-5Y 2.75%, 5Y+ 4.28%.
 • Institutional: 3M '-', all other tenures 2.75%.</t>
@@ -9414,27 +9391,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67421</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>• Individual 3 months to below 2 years 2.75%; '1 year and below 2 years' used as 1 Year.
 • Institutional FD starts at 1 year; &lt;1Y not specified.</t>
@@ -9442,27 +9419,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Ashwin month 2083</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67420</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>• Individual 'Upto 1 Years' 2.80% covers &lt;1Y and 1Y. Locker deposit excluded from saving.
 • Institutional starts 'Above 1 year to 2 year' (2.75%), used as 1 Year; &lt;1Y not specified.</t>
@@ -9470,27 +9447,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Aswin 2083)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67419</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>• FD starts at 1 year for both individual and institutional; &lt;1Y not specified.
 • In-person individual rates used (mobile app rates are 0.10% higher).
@@ -9501,27 +9478,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>1st Ashoj 2083</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67418</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>• 'All other Savings' 2.75% counted once. FCY and current accounts excluded.
 • Institutional 3M and 6M shown as '-'; &lt;1Y not specified.</t>
@@ -9529,27 +9506,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Narayani Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67417</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>• Individual FD: 3-6M 4.75%, 6-12M 4.95%, 12M above 5.15%.
 • Institutional FD: 3-6M N/A, 6-12M 4.95%, 12M above 5.15% (12M above used as 1 Year).</t>
@@ -9557,54 +9534,54 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Ashoj 01, 2083</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67416</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>• FD bands: 3-9 months, One year, Two year and above.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67415</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 1 Year' 2.75% covers both &lt;1Y and 1Y.
 • Institutional: single rate '6 Months and Above' 2.75% applied to all tenures.</t>
@@ -9612,54 +9589,54 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>2083-06-01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67414</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>• Institutional 2.75% is a single rate for 6 months to below 4 years.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Development Banks</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>2083/06/01 (Nepali notice)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67413</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>• Notice in Nepali. Margin account and current account (0.00%) excluded from saving.
 • Individual '1 year to below 5 years' 3.94% used as 1 Year.
@@ -9668,27 +9645,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Aswin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67446</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>• General FD used; 'Three Months to One Year' 2.77% covers &lt;1Y and 1Y.
 • FCY saving (USD/EUR/GBP) excluded. Special FD products excluded.
@@ -9697,27 +9674,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67445</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>• Institutional FD only listed for '24 Months and above' (2.75%); &lt;1Y and 1Y not specified.
 • Individual 1 Year = '12 Months and below 24 Months' 2.90%.
@@ -9726,27 +9703,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Everest Bank Ltd.</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashoj 2083)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67385</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>• Individual 'Above 3 years' corrected from 3.50% to 3.75% per EBL correction notice (17 Sep 2026).
 • '3 months upto 3 years' 2.75% covers &lt;1Y and 1Y.</t>
@@ -9754,27 +9731,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Global IME Bank Ltd.</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67443</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 1 Year' 2.76% used for &lt;1Y and 1Y ('Above 1 Year to below 2 Years' is 2.80%).
 • Institutional only 'Above 1 Year' 2.75%, used for 1Y and &gt;1Y; &lt;1Y not specified.
@@ -9783,27 +9760,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67442</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>• This notice only revises USD FD and fixed-rate loans; it states other deposit rates 'remain as it is'.
 • NPR saving/call/FD rates are not in the notice (see HBL's earlier notice or website).</t>
@@ -9811,27 +9788,27 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Kumari Bank Ltd.</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>01 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67441</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>• In-person individual FD rates used; Kumari Smart app rates are higher (2.80% / 3.73%).
 • '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.</t>
@@ -9839,27 +9816,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67440</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>• 'Personal' term deposit used as Individual FD.
 • Call: notice says 'Negotiable (max 50% of lowest saving rate)'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
@@ -9867,54 +9844,54 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67439</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>• Individual '6 months to below 3 years' 3.00% covers &lt;1Y and 1Y. Recurring deposit excluded from saving.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Nabil Bank Ltd.</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67438</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>• NPR call rate not published; notice says call deposit rate is as per agreement.
 • Individual '6 months to 1 year' 2.85% used as 1 Year ('Above 1 to 2 years' is 3.00%).
@@ -9923,189 +9900,189 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Nepal Bank Ltd.</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>1st Ashwin 2083</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67437</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>• Individual '3M upto 1Y' 2.76% used for &lt;1Y and 1Y ('Above 1Y upto 2Y' is 3.00%).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67436</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67435</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>NMB Bank Ltd.</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Asoj 1, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67434</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>• Institutional '3 Months to Below 1 Year' shown as '-'.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>01st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67433</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026 (01 Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67432</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>• Individual '6 months to 1 year' 2.75% used as 1 Year ('Above 1 year to 3 years' is 3.10%).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>2083 Asoj 01 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67430</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>• Notice in Nepali. General (साधारण) FD used; '1 year to 2 years' 3.15% used as 1 Year.
 • FCY saving excluded.</t>
@@ -10113,108 +10090,108 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Sanima Bank Ltd.</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>Ashwin 1, 2083</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67429</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 12 Months' 2.80% covers &lt;1Y and 1Y; remittance FD excluded.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67428</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67427</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Standard Chartered Bank Nepal Ltd.</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67526</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>• Latest SCB notice (22 Sep 2026) only amends FCY FD rates; NPR rates taken from SCB's 16 Sep notice.
 • Non-individual FD: '1 year and above' 2.75%.</t>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$AB$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$AB$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Development FD Spread'!$A$4:$V$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly History'!$A$1:$N$67</definedName>
   </definedNames>
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB41"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -818,90 +818,90 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Corporate Development Bank Ltd.</t>
+          <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0375</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0375</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.42%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.50%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0275</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0275</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0275</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0275</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>0.055</v>
+        <v>0.0428</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>0.0575</v>
+        <v>0.0441</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>-0.0025</v>
+        <v>-0.0013</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="W6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="AA6" s="8" t="n">
         <v>0.035</v>
-      </c>
-      <c r="Y6" s="9" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="Z6" s="8" t="n">
-        <v>0.0475</v>
-      </c>
-      <c r="AA6" s="8" t="n">
-        <v>0.05</v>
       </c>
       <c r="AB6" s="9" t="n">
         <v>-0.0025</v>
@@ -910,7 +910,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Garima Bikas Bank Ltd.</t>
+          <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0275</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0275</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
@@ -990,19 +990,19 @@
         <v>0</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0275</v>
       </c>
       <c r="AA7" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Green Development Bank Ltd.</t>
+          <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -1015,86 +1015,92 @@
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U8" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="8" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="AA8" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="M8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O8" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>0.0525</v>
-      </c>
-      <c r="R8" s="8" t="n">
-        <v>0.0555</v>
-      </c>
-      <c r="S8" s="9" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X8" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Y8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="8" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="AA8" s="8" t="n">
-        <v>0.0455</v>
-      </c>
       <c r="AB8" s="9" t="n">
-        <v>-0.003</v>
+        <v>-0.0015</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Jyoti Bikas Bank Ltd.</t>
+          <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -1107,62 +1113,68 @@
         <v>0</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.045</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.046</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>-0.0013</v>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
+      </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U9" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W9" s="8" t="n">
         <v>0.0275</v>
@@ -1174,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="AB9" s="9" t="n">
         <v>0</v>
@@ -1186,7 +1198,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Kamana Sewa Bikas Bank Ltd.</t>
+          <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -1199,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0</v>
@@ -1220,32 +1232,38 @@
       <c r="J10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M10" s="9" t="n">
-        <v>0</v>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N10" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.043</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.045</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>-0.0013</v>
+        <v>-0.002</v>
       </c>
       <c r="T10" s="11" t="inlineStr">
         <is>
@@ -1272,19 +1290,19 @@
         <v>0</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0425</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0445</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>-0.0015</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Lumbini Bikas Bank Ltd.</t>
+          <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -1300,60 +1318,58 @@
         <v>0.028</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.00%</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.00%</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0428</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>0.046</v>
+        <v>0.0441</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>-0.001</v>
+        <v>-0.0013</v>
       </c>
       <c r="T11" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+      <c r="U11" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="V11" s="11" t="inlineStr">
         <is>
@@ -1370,19 +1386,19 @@
         <v>0</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0325</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Mahalaxmi Bikas Bank Ltd.</t>
+          <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -1405,64 +1421,52 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>0.043</v>
+        <v>0.0428</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0441</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U12" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.0013</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W12" s="8" t="n">
         <v>0.0275</v>
@@ -1474,19 +1478,19 @@
         <v>0</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0275</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.0275</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Muktinath Bikas Bank Ltd.</t>
+          <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -1499,22 +1503,22 @@
         <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0325</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0325</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.00%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.00%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
@@ -1530,35 +1534,31 @@
         <v>0</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0459</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.0459</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>-0.0013</v>
-      </c>
-      <c r="T13" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="U13" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="V13" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W13" s="8" t="n">
         <v>0.0275</v>
@@ -1570,194 +1570,136 @@
         <v>0</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="AA13" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.035</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Narayani Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>1.375%</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>1.375%</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>0.0495</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="S14" s="9" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v>0.0495</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="W14" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="X14" s="8" t="n">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="Z14" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="AA14" s="8" t="n">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="AB14" s="9" t="n">
-        <v>-0.0025</v>
-      </c>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="6" t="n"/>
+      <c r="T14" s="6" t="n"/>
+      <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="6" t="n"/>
+      <c r="Z14" s="6" t="n"/>
+      <c r="AA14" s="6" t="n"/>
+      <c r="AB14" s="6" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Salapa Bikas Bank Ltd.</t>
+          <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0277</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0278</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0304</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0339</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0</v>
+        <v>-0.0035</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0277</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0278</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0277</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0278</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>0.055</v>
+        <v>0.0415</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>0.055</v>
+        <v>0.0415</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0275</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0275</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0275</v>
       </c>
       <c r="X15" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0275</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0275</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0275</v>
       </c>
       <c r="AB15" s="9" t="n">
         <v>0</v>
@@ -1766,7 +1708,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Shangri-la Development Bank Ltd.</t>
+          <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -1779,86 +1721,98 @@
         <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0285</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0285</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0385</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.0385</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>-0.0013</v>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y16" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U16" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V16" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="X16" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="Y16" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Z16" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>0</v>
+        <v>-0.0025</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Shine Resunga Development Bank Ltd.</t>
+          <t>Everest Bank Ltd.</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -1871,297 +1825,385 @@
         <v>0</v>
       </c>
       <c r="E17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.50%</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.50%</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="8" t="n">
         <v>0.0325</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.37%</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.37%</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="P17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="S17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="8" t="n">
-        <v>0.035</v>
       </c>
       <c r="AA17" s="8" t="n">
         <v>0.035</v>
       </c>
       <c r="AB17" s="9" t="n">
-        <v>0</v>
+        <v>-0.0025</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Sindhu Bikash Bank Ltd.</t>
+          <t>Global IME Bank Ltd.</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="C18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="W18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA18" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AB18" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Himalayan Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.37%</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N18" s="8" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>0.0441</v>
-      </c>
-      <c r="P18" s="9" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="R18" s="8" t="n">
-        <v>0.0441</v>
-      </c>
-      <c r="S18" s="9" t="n">
-        <v>-0.0013</v>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U18" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V18" s="11" t="inlineStr">
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X18" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="Y18" s="11" t="inlineStr">
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Z18" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA18" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="AB18" s="11" t="inlineStr">
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
-      <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="n"/>
-      <c r="S19" s="6" t="n"/>
-      <c r="T19" s="6" t="n"/>
-      <c r="U19" s="6" t="n"/>
-      <c r="V19" s="6" t="n"/>
-      <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
-      <c r="AA19" s="6" t="n"/>
-      <c r="AB19" s="6" t="n"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="X19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="Y19" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="AA19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="AB19" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Agricultural Development Bank Ltd.</t>
+          <t>Kumari Bank Ltd.</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.0275</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0275</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0.0304</v>
+        <v>0.0391</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.0339</v>
+        <v>0.0391</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>-0.0035</v>
+        <v>0</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>Up to 0.81%</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>Up to 0.81%</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.0275</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0275</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.0275</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0275</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.0343</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.0346</v>
       </c>
       <c r="S20" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="T20" s="8" t="n">
         <v>0.0275</v>
@@ -2182,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0301</v>
       </c>
       <c r="AA20" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0301</v>
       </c>
       <c r="AB20" s="9" t="n">
         <v>0</v>
@@ -2194,7 +2236,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Citizens Bank International Ltd.</t>
+          <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -2229,135 +2271,123 @@
         <v>0</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.029</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.029</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.04</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>0.0385</v>
+        <v>0.04</v>
       </c>
       <c r="S21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U21" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="X21" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="Y21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y21" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="AA21" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0325</v>
       </c>
       <c r="AB21" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Everest Bank Ltd.</t>
+          <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0</v>
+        <v>-0.0001</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0301</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0</v>
+        <v>-0.0021</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.50%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.50%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="M22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="P22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.045</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.045</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="T22" s="8" t="n">
         <v>0.0275</v>
@@ -2378,19 +2408,19 @@
         <v>0</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.03</v>
       </c>
       <c r="AA22" s="8" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="AB22" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Global IME Bank Ltd.</t>
+          <t>Nabil Bank Ltd.</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -2403,10 +2433,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
@@ -2425,46 +2455,40 @@
         <v>0</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0285</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0285</v>
       </c>
       <c r="M23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0285</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0285</v>
       </c>
       <c r="P23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0425</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0455</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U23" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.003</v>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V23" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W23" s="8" t="n">
         <v>0.0275</v>
@@ -2476,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0301</v>
       </c>
       <c r="AA23" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0301</v>
       </c>
       <c r="AB23" s="9" t="n">
         <v>0</v>
@@ -2488,149 +2512,99 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Himalayan Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="O24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="P24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="S24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="X24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="Y24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="AA24" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="AB24" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Nepal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AA24" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AB24" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Kumari Bank Ltd.</t>
+          <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -2643,22 +2617,22 @@
         <v>0</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0275</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0275</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.81%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.81%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
@@ -2683,13 +2657,13 @@
         <v>0</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>0.0343</v>
+        <v>0.04</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.04</v>
       </c>
       <c r="S25" s="9" t="n">
-        <v>-0.0003</v>
+        <v>0</v>
       </c>
       <c r="T25" s="8" t="n">
         <v>0.0275</v>
@@ -2710,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.03</v>
       </c>
       <c r="AA25" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.03</v>
       </c>
       <c r="AB25" s="9" t="n">
         <v>0</v>
@@ -2722,7 +2696,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank Ltd.</t>
+          <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
@@ -2735,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0375</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0375</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.35%</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.35%</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
@@ -2775,22 +2749,28 @@
         <v>0</v>
       </c>
       <c r="Q26" s="8" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="R26" s="8" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="S26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V26" s="9" t="n">
-        <v>0</v>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U26" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W26" s="8" t="n">
         <v>0.0275</v>
@@ -2802,10 +2782,10 @@
         <v>0</v>
       </c>
       <c r="Z26" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.035</v>
       </c>
       <c r="AA26" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.035</v>
       </c>
       <c r="AB26" s="9" t="n">
         <v>0</v>
@@ -2814,54 +2794,54 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank Ltd.</t>
+          <t>NMB Bank Ltd.</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>-0.0021</v>
+        <v>0</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="M27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="P27" s="9" t="n">
         <v>0</v>
@@ -2875,14 +2855,18 @@
       <c r="S27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="8" t="n">
-        <v>0.0275</v>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>0</v>
+      <c r="V27" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W27" s="8" t="n">
         <v>0.0275</v>
@@ -2894,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="AA27" s="8" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="AB27" s="9" t="n">
         <v>0</v>
@@ -2906,66 +2890,66 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Nabil Bank Ltd.</t>
+          <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0302</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0302</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.029</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.029</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.03</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.03</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.04</v>
       </c>
       <c r="R28" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.04</v>
       </c>
       <c r="S28" s="9" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="T28" s="8" t="n">
         <v>0.0275</v>
@@ -2986,10 +2970,10 @@
         <v>0</v>
       </c>
       <c r="Z28" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="AA28" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="AB28" s="9" t="n">
         <v>0</v>
@@ -2998,63 +2982,63 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Nepal Bank Ltd.</t>
+          <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.03</v>
       </c>
       <c r="F29" s="8" t="n">
         <v>0.03</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>Up to 0.10%</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>Up to 0.10%</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="M29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="P29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.0455</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.0455</v>
       </c>
       <c r="S29" s="9" t="n">
         <v>0</v>
@@ -3078,10 +3062,10 @@
         <v>0</v>
       </c>
       <c r="Z29" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="AA29" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="AB29" s="9" t="n">
         <v>0</v>
@@ -3090,7 +3074,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>NIC Asia Bank Ltd.</t>
+          <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
@@ -3103,41 +3087,41 @@
         <v>0</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="M30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0315</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0315</v>
       </c>
       <c r="P30" s="9" t="n">
         <v>0</v>
@@ -3182,7 +3166,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank Ltd.</t>
+          <t>Sanima Bank Ltd.</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -3195,41 +3179,41 @@
         <v>0</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.028</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.028</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.35%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.35%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="O31" s="8" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="P31" s="9" t="n">
         <v>0</v>
@@ -3243,20 +3227,14 @@
       <c r="S31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T31" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U31" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V31" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="T31" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W31" s="8" t="n">
         <v>0.0275</v>
@@ -3268,19 +3246,19 @@
         <v>0</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0351</v>
       </c>
       <c r="AA31" s="8" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="AB31" s="9" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>NMB Bank Ltd.</t>
+          <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
@@ -3293,66 +3271,62 @@
         <v>0</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0279</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0279</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.75%</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.75%</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.032</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.032</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>0.045</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>0.045</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="S32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+      <c r="T32" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="U32" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="V32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="V32" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W32" s="8" t="n">
         <v>0.0275</v>
@@ -3364,10 +3338,10 @@
         <v>0</v>
       </c>
       <c r="Z32" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="AA32" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="AB32" s="9" t="n">
         <v>0</v>
@@ -3376,75 +3350,81 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank Ltd.</t>
+          <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>0.0302</v>
+        <v>0.0305</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.0302</v>
+        <v>0.0305</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="M33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="P33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="8" t="n">
-        <v>0.04</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>0.04</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="S33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T33" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V33" s="9" t="n">
-        <v>0</v>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U33" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W33" s="8" t="n">
         <v>0.0275</v>
@@ -3456,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0305</v>
       </c>
       <c r="AA33" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0305</v>
       </c>
       <c r="AB33" s="9" t="n">
         <v>0</v>
@@ -3468,7 +3448,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Prabhu Bank Ltd.</t>
+          <t>Standard Chartered Bank Nepal Ltd.</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
@@ -3481,26 +3461,26 @@
         <v>0</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.10%</t>
+          <t>Up to 0.20%</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.10%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="K34" s="8" t="n">
         <v>0.0275</v>
@@ -3521,22 +3501,28 @@
         <v>0</v>
       </c>
       <c r="Q34" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0375</v>
       </c>
       <c r="R34" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.038</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
+      </c>
+      <c r="T34" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="U34" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W34" s="8" t="n">
         <v>0.0275</v>
@@ -3557,498 +3543,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Rastriya Banijya Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="8" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="O35" s="8" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="P35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AA35" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AB35" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Sanima Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="P36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="R36" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="S36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="8" t="n">
-        <v>0.0351</v>
-      </c>
-      <c r="AA36" s="8" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="AB36" s="9" t="n">
-        <v>0.0021</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Nepal SBI Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0.0279</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>0.0279</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.75%</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.75%</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="8" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="P37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="8" t="n">
-        <v>0.04099999999999999</v>
-      </c>
-      <c r="R37" s="8" t="n">
-        <v>0.04099999999999999</v>
-      </c>
-      <c r="S37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X37" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA37" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AB37" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Siddhartha Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="G38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.25%</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.25%</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O38" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>0.03759999999999999</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>0.03759999999999999</v>
-      </c>
-      <c r="S38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U38" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V38" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="8" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="AA38" s="8" t="n">
-        <v>0.0305</v>
-      </c>
-      <c r="AB38" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Standard Chartered Bank Nepal Ltd.</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.20%</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.25%</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="K39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="S39" s="9" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="T39" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U39" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V39" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="Y39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AA39" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="AB39" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AB39"/>
+  <autoFilter ref="A4:AB34"/>
   <mergeCells count="8">
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="A19:AB19"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:AB5"/>
     <mergeCell ref="K3:S3"/>
+    <mergeCell ref="A14:AB14"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="T3:AB3"/>
     <mergeCell ref="H3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D39">
+  <conditionalFormatting sqref="D5:D34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(D5),D5&gt;0)</formula>
     </cfRule>
@@ -4062,7 +3576,7 @@
       <formula>D5="Changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G39">
+  <conditionalFormatting sqref="G5:G34">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(ISNUMBER(G5),G5&gt;0)</formula>
     </cfRule>
@@ -4076,7 +3590,7 @@
       <formula>G5="Changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J39">
+  <conditionalFormatting sqref="J5:J34">
     <cfRule type="expression" priority="9" dxfId="0">
       <formula>AND(ISNUMBER(J5),J5&gt;0)</formula>
     </cfRule>
@@ -4090,7 +3604,7 @@
       <formula>J5="Changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M39">
+  <conditionalFormatting sqref="M5:M34">
     <cfRule type="expression" priority="13" dxfId="0">
       <formula>AND(ISNUMBER(M5),M5&gt;0)</formula>
     </cfRule>
@@ -4104,7 +3618,7 @@
       <formula>M5="Changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P39">
+  <conditionalFormatting sqref="P5:P34">
     <cfRule type="expression" priority="17" dxfId="0">
       <formula>AND(ISNUMBER(P5),P5&gt;0)</formula>
     </cfRule>
@@ -4118,7 +3632,7 @@
       <formula>P5="Changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S39">
+  <conditionalFormatting sqref="S5:S34">
     <cfRule type="expression" priority="21" dxfId="0">
       <formula>AND(ISNUMBER(S5),S5&gt;0)</formula>
     </cfRule>
@@ -4132,7 +3646,7 @@
       <formula>S5="Changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V39">
+  <conditionalFormatting sqref="V5:V34">
     <cfRule type="expression" priority="25" dxfId="0">
       <formula>AND(ISNUMBER(V5),V5&gt;0)</formula>
     </cfRule>
@@ -4146,7 +3660,7 @@
       <formula>V5="Changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y5:Y39">
+  <conditionalFormatting sqref="Y5:Y34">
     <cfRule type="expression" priority="29" dxfId="0">
       <formula>AND(ISNUMBER(Y5),Y5&gt;0)</formula>
     </cfRule>
@@ -4160,7 +3674,7 @@
       <formula>Y5="Changed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB5:AB39">
+  <conditionalFormatting sqref="AB5:AB34">
     <cfRule type="expression" priority="33" dxfId="0">
       <formula>AND(ISNUMBER(AB5),AB5&gt;0)</formula>
     </cfRule>
@@ -9224,7 +8738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9279,7 +8793,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Corporate Development Bank Ltd.</t>
+          <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -9289,44 +8803,15 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>1 Ashwin 2083 (17 Sep 2026)</t>
+          <t>2083.06.01 (17 Sep 2026)</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67425</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67424</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>• Individual FD: 3M 3.50%, 6-9M 3.75%, 1Y 4.25%, &gt;1-2Y 4.50%, &gt;2-3Y 5.00%, &gt;3-5Y 5.25%, &gt;5Y 5.50%.
-• Corporate (institutional) FD minimum 6 months: 6-9M 2.85%, 1Y 3.25%, &gt;5Y 4.75%.
-• Saving includes Staff Saving (4.10%, highest) - excluded as first highest per rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Garima Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>2083.06.01 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67424</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>• Individual '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.
 • Institutional '6 Months to Below 3 Years' 2.75% covers &lt;1Y and 1Y.
@@ -9334,10 +8819,38 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Jyoti Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67422</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>• Individual: 3M 2.75%, 6M to below 3Y 2.75%, 3-5Y 2.75%, 5Y+ 4.28%.
+• Institutional: 3M '-', all other tenures 2.75%.</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Green Development Bank Ltd.</t>
+          <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -9347,25 +8860,25 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>1st Ashoj 2083</t>
+          <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67423</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67421</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>• FD bands: 3 Month, 6 Month, 1 Year to below 2 years, 2 to below 4 years, 4 years and above.
-• Institutional 3 Month shown as '-'; 6 Month 2.75% used as &lt;1Y max.</t>
+          <t>• Individual 3 months to below 2 years 2.75%; '1 year and below 2 years' used as 1 Year.
+• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Jyoti Bikas Bank Ltd.</t>
+          <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -9375,25 +8888,25 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>Ashwin month 2083</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67422</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67420</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>• Individual: 3M 2.75%, 6M to below 3Y 2.75%, 3-5Y 2.75%, 5Y+ 4.28%.
-• Institutional: 3M '-', all other tenures 2.75%.</t>
+          <t>• Individual 'Upto 1 Years' 2.80% covers &lt;1Y and 1Y. Locker deposit excluded from saving.
+• Institutional starts 'Above 1 year to 2 year' (2.75%), used as 1 Year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Kamana Sewa Bikas Bank Ltd.</t>
+          <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -9403,71 +8916,15 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+          <t>17 Sep 2026 (1st Aswin 2083)</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67421</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67419</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>• Individual 3 months to below 2 years 2.75%; '1 year and below 2 years' used as 1 Year.
-• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Lumbini Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin month 2083</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67420</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>• Individual 'Upto 1 Years' 2.80% covers &lt;1Y and 1Y. Locker deposit excluded from saving.
-• Institutional starts 'Above 1 year to 2 year' (2.75%), used as 1 Year; &lt;1Y not specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Mahalaxmi Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026 (1st Aswin 2083)</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67419</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>• FD starts at 1 year for both individual and institutional; &lt;1Y not specified.
 • In-person individual rates used (mobile app rates are 0.10% higher).
@@ -9477,10 +8934,66 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Muktinath Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>1st Ashoj 2083</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67418</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>• 'All other Savings' 2.75% counted once. FCY and current accounts excluded.
+• Institutional 3M and 6M shown as '-'; &lt;1Y not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Shangri-la Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Development Banks</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67415</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>• Individual '3 Months to 1 Year' 2.75% covers both &lt;1Y and 1Y.
+• Institutional: single rate '6 Months and Above' 2.75% applied to all tenures.</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Muktinath Bikas Bank Ltd.</t>
+          <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -9490,182 +9003,42 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>1st Ashoj 2083</t>
+          <t>2083-06-01 (17 Sep 2026)</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67418</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67414</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>• 'All other Savings' 2.75% counted once. FCY and current accounts excluded.
-• Institutional 3M and 6M shown as '-'; &lt;1Y not specified.</t>
+          <t>• Institutional 2.75% is a single rate for 6 months to below 4 years.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Narayani Development Bank Ltd.</t>
+          <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Development Banks</t>
+          <t>Commercial Banks</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>Aswin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67417</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67446</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>• Individual FD: 3-6M 4.75%, 6-12M 4.95%, 12M above 5.15%.
-• Institutional FD: 3-6M N/A, 6-12M 4.95%, 12M above 5.15% (12M above used as 1 Year).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Salapa Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Ashoj 01, 2083</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67416</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>• FD bands: 3-9 months, One year, Two year and above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Shangri-la Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67415</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '3 Months to 1 Year' 2.75% covers both &lt;1Y and 1Y.
-• Institutional: single rate '6 Months and Above' 2.75% applied to all tenures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Shine Resunga Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>2083-06-01 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67414</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>• Institutional 2.75% is a single rate for 6 months to below 4 years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Sindhu Bikash Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>2083/06/01 (Nepali notice)</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67413</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>• Notice in Nepali. Margin account and current account (0.00%) excluded from saving.
-• Individual '1 year to below 5 years' 3.94% used as 1 Year.
-• Institutional: single rate '6 months or above' 2.75% applied to all tenures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Agricultural Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>Aswin 01, 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67446</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>• General FD used; 'Three Months to One Year' 2.77% covers &lt;1Y and 1Y.
 • FCY saving (USD/EUR/GBP) excluded. Special FD products excluded.
@@ -9673,28 +9046,28 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67445</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>• Institutional FD only listed for '24 Months and above' (2.75%); &lt;1Y and 1Y not specified.
 • Individual 1 Year = '12 Months and below 24 Months' 2.90%.
@@ -9702,56 +9075,56 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Everest Bank Ltd.</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashoj 2083)</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67385</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>• Individual 'Above 3 years' corrected from 3.50% to 3.75% per EBL correction notice (17 Sep 2026).
 • '3 months upto 3 years' 2.75% covers &lt;1Y and 1Y.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Global IME Bank Ltd.</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67443</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>• Individual '3 Months to 1 Year' 2.76% used for &lt;1Y and 1Y ('Above 1 Year to below 2 Years' is 2.80%).
 • Institutional only 'Above 1 Year' 2.75%, used for 1Y and &gt;1Y; &lt;1Y not specified.
@@ -9759,139 +9132,139 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67442</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>• This notice only revises USD FD and fixed-rate loans; it states other deposit rates 'remain as it is'.
 • NPR saving/call/FD rates are not in the notice (see HBL's earlier notice or website).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Kumari Bank Ltd.</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>01 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67441</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>• In-person individual FD rates used; Kumari Smart app rates are higher (2.80% / 3.73%).
 • '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67440</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>• 'Personal' term deposit used as Individual FD.
 • Call: notice says 'Negotiable (max 50% of lowest saving rate)'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67439</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>• Individual '6 months to below 3 years' 3.00% covers &lt;1Y and 1Y. Recurring deposit excluded from saving.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Nabil Bank Ltd.</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Commercial Banks</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>17 Sep 2026 (1 Ashwin 2083)</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>https://merolagani.com/AnnouncementDetail.aspx?id=67438</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>• NPR call rate not published; notice says call deposit rate is as per agreement.
 • Individual '6 months to 1 year' 2.85% used as 1 Year ('Above 1 to 2 years' is 3.00%).
@@ -9899,10 +9272,145 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Nepal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>1st Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67437</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>• Individual '3M upto 1Y' 2.76% used for &lt;1Y and 1Y ('Above 1Y upto 2Y' is 3.00%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>NIC Asia Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67436</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67435</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>NMB Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Asoj 1, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67434</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>• Institutional '3 Months to Below 1 Year' shown as '-'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>01st Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67433</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Nepal Bank Ltd.</t>
+          <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -9912,24 +9420,24 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>1st Ashwin 2083</t>
+          <t>17 Sep 2026 (01 Ashwin 2083)</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67437</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67432</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>• Individual '3M upto 1Y' 2.76% used for &lt;1Y and 1Y ('Above 1Y upto 2Y' is 3.00%).</t>
+          <t>• Individual '6 months to 1 year' 2.75% used as 1 Year ('Above 1 year to 3 years' is 3.10%).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>NIC Asia Bank Ltd.</t>
+          <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -9939,24 +9447,25 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+          <t>2083 Asoj 01 (17 Sep 2026)</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67436</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67430</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>• Notice in Nepali. General (साधारण) FD used; '1 year to 2 years' 3.15% used as 1 Year.
+• FCY saving excluded.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank Ltd.</t>
+          <t>Sanima Bank Ltd.</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -9966,24 +9475,24 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+          <t>Ashwin 1, 2083</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67435</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67429</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
+          <t>• Individual '3 Months to 12 Months' 2.80% covers &lt;1Y and 1Y; remittance FD excluded.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>NMB Bank Ltd.</t>
+          <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -9993,24 +9502,24 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Asoj 1, 2083 (17 Sep 2026)</t>
+          <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67434</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67428</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>• Institutional '3 Months to Below 1 Year' shown as '-'.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank Ltd.</t>
+          <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -10020,24 +9529,24 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>01st Ashwin 2083 (17 Sep 2026)</t>
+          <t>17 Sep 2026</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67433</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67427</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Prabhu Bank Ltd.</t>
+          <t>Standard Chartered Bank Nepal Ltd.</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -10047,151 +9556,15 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (01 Ashwin 2083)</t>
+          <t>17 Sep 2026</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67432</t>
+          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67526</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '6 months to 1 year' 2.75% used as 1 Year ('Above 1 year to 3 years' is 3.10%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Rastriya Banijya Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>2083 Asoj 01 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67430</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>• Notice in Nepali. General (साधारण) FD used; '1 year to 2 years' 3.15% used as 1 Year.
-• FCY saving excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Sanima Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin 1, 2083</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67429</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '3 Months to 12 Months' 2.80% covers &lt;1Y and 1Y; remittance FD excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Nepal SBI Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026 (1st Ashwin 2083)</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67428</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Siddhartha Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67427</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Standard Chartered Bank Nepal Ltd.</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67526</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>• Latest SCB notice (22 Sep 2026) only amends FCY FD rates; NPR rates taken from SCB's 16 Sep notice.
 • Non-individual FD: '1 year and above' 2.75%.</t>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$AB$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Development FD Spread'!$A$4:$V$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Development FD Spread'!$A$4:$V$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly History'!$A$1:$N$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3698,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3899,81 +3899,81 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Corporate Development Bank Ltd.</t>
+          <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="N5" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0.0285</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="I5" s="8" t="n">
+      <c r="O5" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="U5" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="J5" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="P5" s="9" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>0.0525</v>
-      </c>
-      <c r="R5" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v>0.0475</v>
-      </c>
       <c r="V5" s="9" t="n">
-        <v>0.0075</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Garima Bikas Bank Ltd.</t>
+          <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -4008,124 +4008,128 @@
         <v>0</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.0025</v>
+        <v>0</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="T6" s="8" t="n">
         <v>0.0428</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0275</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0.0103</v>
+        <v>0.0153</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Green Development Bank Ltd.</t>
+          <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>0.0475</v>
-      </c>
       <c r="L7" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0275</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.01</v>
+        <v>0.0025</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>0.0475</v>
+        <v>0.0315</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0275</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>0.0525</v>
+        <v>0.0315</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0335</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>0.01</v>
+        <v>-0.002</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>0.0525</v>
+        <v>0.0428</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0335</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0.01</v>
+        <v>0.009299999999999999</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Jyoti Bikas Bank Ltd.</t>
+          <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
@@ -4138,68 +4142,74 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>0.028</v>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.034</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.045</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0.0153</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Kamana Sewa Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>0.0275</v>
+          <t>Mahalaxmi Bikas Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -4211,8 +4221,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
-        <v>0.0275</v>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
@@ -4225,139 +4237,137 @@
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.0025</v>
+        <v>0.003</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>0.0315</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.032</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0.0315</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.032</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>-0.002</v>
+        <v>0.005</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.043</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0425</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Lumbini Bikas Bank Ltd.</t>
+          <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>0.028</v>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>0.0275</v>
-      </c>
       <c r="M10" s="9" t="n">
-        <v>0.0015</v>
+        <v>0.002</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>0.029</v>
+        <v>0.035</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>0.03</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.001</v>
+        <v>0.005</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.03</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0428</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0.015</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Mahalaxmi Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+          <t>Shangri-la Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
@@ -4369,75 +4379,71 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.003</v>
+        <v>0.0025</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0275</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>0.005</v>
+        <v>0.0025</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0275</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>0.005</v>
+        <v>0.0075</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>0.043</v>
+        <v>0.0428</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0275</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.0153</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Muktinath Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>0.0275</v>
+          <t>Shine Resunga Development Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
@@ -4452,439 +4458,67 @@
       <c r="E12" s="8" t="n">
         <v>0.0275</v>
       </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F12" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0325</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>0.005</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0375</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0325</v>
       </c>
       <c r="S12" s="9" t="n">
         <v>0.005</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0459</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0.0108</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Narayani Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>0.0475</v>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.0495</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0.0495</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>0.0495</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>0.0495</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="P13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="S13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="V13" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Salapa Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S14" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v>0.005</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Shangri-la Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P15" s="9" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="Q15" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="S15" s="9" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V15" s="9" t="n">
-        <v>0.0153</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Shine Resunga Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N16" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P16" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q16" s="8" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="R16" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="S16" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="V16" s="9" t="n">
         <v>0.0109</v>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Sindhu Bikash Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="P17" s="9" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="S17" s="9" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="V17" s="9" t="n">
-        <v>0.0153</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Difference = Individual rate minus Institutional rate (percentage points): green = individuals earn more, red = institutions earn more, grey = same. 'Not specified' = the bank publishes no rate for that tenure (e.g. institutional FD starting at 6 months or 1 year). Rates are the general FD rate applying to a deposit of exactly that tenure; '5 Years &amp; Above' uses the band covering 5 years.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V17"/>
+  <autoFilter ref="A4:V12"/>
   <mergeCells count="9">
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A1:V1"/>
@@ -4896,7 +4530,7 @@
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="Q3:S3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D17">
+  <conditionalFormatting sqref="D5:D12">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(D5),D5&gt;0)</formula>
     </cfRule>
@@ -4907,7 +4541,7 @@
       <formula>AND(ISNUMBER(D5),D5=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G17">
+  <conditionalFormatting sqref="G5:G12">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>AND(ISNUMBER(G5),G5&gt;0)</formula>
     </cfRule>
@@ -4918,7 +4552,7 @@
       <formula>AND(ISNUMBER(G5),G5=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J17">
+  <conditionalFormatting sqref="J5:J12">
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>AND(ISNUMBER(J5),J5&gt;0)</formula>
     </cfRule>
@@ -4929,7 +4563,7 @@
       <formula>AND(ISNUMBER(J5),J5=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M17">
+  <conditionalFormatting sqref="M5:M12">
     <cfRule type="expression" priority="10" dxfId="0">
       <formula>AND(ISNUMBER(M5),M5&gt;0)</formula>
     </cfRule>
@@ -4940,7 +4574,7 @@
       <formula>AND(ISNUMBER(M5),M5=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P17">
+  <conditionalFormatting sqref="P5:P12">
     <cfRule type="expression" priority="13" dxfId="0">
       <formula>AND(ISNUMBER(P5),P5&gt;0)</formula>
     </cfRule>
@@ -4951,7 +4585,7 @@
       <formula>AND(ISNUMBER(P5),P5=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S17">
+  <conditionalFormatting sqref="S5:S12">
     <cfRule type="expression" priority="16" dxfId="0">
       <formula>AND(ISNUMBER(S5),S5&gt;0)</formula>
     </cfRule>
@@ -4962,7 +4596,7 @@
       <formula>AND(ISNUMBER(S5),S5=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V17">
+  <conditionalFormatting sqref="V5:V12">
     <cfRule type="expression" priority="19" dxfId="0">
       <formula>AND(ISNUMBER(V5),V5&gt;0)</formula>
     </cfRule>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interest Rate Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Development FD Spread" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly History" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$AB$34</definedName>
@@ -111,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -142,9 +141,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8364,848 +8360,4 @@
   <autoFilter ref="A1:N67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="100" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Effective Date</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Source Document</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Notes (Ashwin 2083)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>All banks</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr"/>
-      <c r="C2" s="14" t="inlineStr"/>
-      <c r="D2" s="14" t="inlineStr"/>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>Saving Max is the second highest saving rate, excluding the first highest. Call and FCY accounts are excluded from saving rates; loan, base and spread rates are excluded. Remittance FD rates are excluded from Individual FD. Where no direct call rate is published (negotiable / as per agreement / 50% of saving rate), Call = 'Up to' 50% of the lowest saving rate. Months follow the Nepali calendar (Shrawan to Ashadh).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Garima Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>2083.06.01 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67424</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.
-• Institutional '6 Months to Below 3 Years' 2.75% covers &lt;1Y and 1Y.
-• Current, margin and FCY saving accounts excluded from saving.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Jyoti Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67422</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>• Individual: 3M 2.75%, 6M to below 3Y 2.75%, 3-5Y 2.75%, 5Y+ 4.28%.
-• Institutional: 3M '-', all other tenures 2.75%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Kamana Sewa Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>1st Ashwin 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67421</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>• Individual 3 months to below 2 years 2.75%; '1 year and below 2 years' used as 1 Year.
-• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Lumbini Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin month 2083</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67420</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>• Individual 'Upto 1 Years' 2.80% covers &lt;1Y and 1Y. Locker deposit excluded from saving.
-• Institutional starts 'Above 1 year to 2 year' (2.75%), used as 1 Year; &lt;1Y not specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Mahalaxmi Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026 (1st Aswin 2083)</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67419</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>• FD starts at 1 year for both individual and institutional; &lt;1Y not specified.
-• In-person individual rates used (mobile app rates are 0.10% higher).
-• Dollar account, margin locker and PMS accounts excluded from saving.
-• No call rate published; notice says call deposit rate is as per NRB guidelines.
-• Call: notice says 'As per NRB guidelines'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Muktinath Bikas Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>1st Ashoj 2083</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67418</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>• 'All other Savings' 2.75% counted once. FCY and current accounts excluded.
-• Institutional 3M and 6M shown as '-'; &lt;1Y not specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Shangri-la Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67415</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '3 Months to 1 Year' 2.75% covers both &lt;1Y and 1Y.
-• Institutional: single rate '6 Months and Above' 2.75% applied to all tenures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Shine Resunga Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Development Banks</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>2083-06-01 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67414</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>• Institutional 2.75% is a single rate for 6 months to below 4 years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Agricultural Development Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Aswin 01, 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67446</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>• General FD used; 'Three Months to One Year' 2.77% covers &lt;1Y and 1Y.
-• FCY saving (USD/EUR/GBP) excluded. Special FD products excluded.
-• Institutional: single rate 'Six Months and Above' 2.75% applied to all tenures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Citizens Bank International Ltd.</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>1 Ashwin 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67445</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>• Institutional FD only listed for '24 Months and above' (2.75%); &lt;1Y and 1Y not specified.
-• Individual 1 Year = '12 Months and below 24 Months' 2.90%.
-• Call: notice says 'Negotiable as per NRB Directive'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Everest Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026 (1 Ashoj 2083)</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67385</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>• Individual 'Above 3 years' corrected from 3.50% to 3.75% per EBL correction notice (17 Sep 2026).
-• '3 months upto 3 years' 2.75% covers &lt;1Y and 1Y.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Global IME Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67443</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '3 Months to 1 Year' 2.76% used for &lt;1Y and 1Y ('Above 1 Year to below 2 Years' is 2.80%).
-• Institutional only 'Above 1 Year' 2.75%, used for 1Y and &gt;1Y; &lt;1Y not specified.
-• Call: notice says 'Up to 50% of minimum saving deposit rate'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Himalayan Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67442</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>• This notice only revises USD FD and fixed-rate loans; it states other deposit rates 'remain as it is'.
-• NPR saving/call/FD rates are not in the notice (see HBL's earlier notice or website).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Kumari Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>01 Ashwin 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67441</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>• In-person individual FD rates used; Kumari Smart app rates are higher (2.80% / 3.73%).
-• '3 Months to below 2 Years' 2.75% covers &lt;1Y and 1Y.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Laxmi Sunrise Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67440</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>• 'Personal' term deposit used as Individual FD.
-• Call: notice says 'Negotiable (max 50% of lowest saving rate)'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Machhapuchchhre Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67439</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '6 months to below 3 years' 3.00% covers &lt;1Y and 1Y. Recurring deposit excluded from saving.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Nabil Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026 (1 Ashwin 2083)</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67438</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>• NPR call rate not published; notice says call deposit rate is as per agreement.
-• Individual '6 months to 1 year' 2.85% used as 1 Year ('Above 1 to 2 years' is 3.00%).
-• Call: notice says 'As per agreement'; shown as 50% of lowest saving rate (2.75%) = Up to 1.375%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Nepal Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>1st Ashwin 2083</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67437</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '3M upto 1Y' 2.76% used for &lt;1Y and 1Y ('Above 1Y upto 2Y' is 3.00%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>NIC Asia Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>1st Ashwin 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67436</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Nepal Investment Mega Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026 (1st Ashwin 2083)</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67435</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>NMB Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>Asoj 1, 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67434</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>• Institutional '3 Months to Below 1 Year' shown as '-'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Prime Commercial Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>01st Ashwin 2083 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67433</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Prabhu Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026 (01 Ashwin 2083)</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67432</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '6 months to 1 year' 2.75% used as 1 Year ('Above 1 year to 3 years' is 3.10%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Rastriya Banijya Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>2083 Asoj 01 (17 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67430</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>• Notice in Nepali. General (साधारण) FD used; '1 year to 2 years' 3.15% used as 1 Year.
-• FCY saving excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Sanima Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>Ashwin 1, 2083</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67429</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>• Individual '3 Months to 12 Months' 2.80% covers &lt;1Y and 1Y; remittance FD excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Nepal SBI Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026 (1st Ashwin 2083)</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67428</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Siddhartha Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67427</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>• Institutional FD starts at 1 year; &lt;1Y not specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>Standard Chartered Bank Nepal Ltd.</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Commercial Banks</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>17 Sep 2026</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>https://merolagani.com/AnnouncementDetail.aspx?id=67526</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>• Latest SCB notice (22 Sep 2026) only amends FCY FD rates; NPR rates taken from SCB's 16 Sep notice.
-• Non-individual FD: '1 year and above' 2.75%.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$AB$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Development FD Spread'!$A$4:$V$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly History'!$A$1:$N$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly History'!$A$1:$N$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2001,140 +2001,90 @@
           <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="P19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="R19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="U19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="X19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="Y19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="AA19" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="AB19" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B19" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="Y19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AA19" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AB19" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -4613,7 +4563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6031,56 +5981,44 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Shrawan 2083</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+      <c r="H26" s="8" t="n">
+        <v>0.0276</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.046</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>0.0441</v>
-      </c>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L26" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M26" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.046</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>2083/05/01 (Nepali notice)</t>
+          <t>2083/04/01 (Nepali notice)</t>
         </is>
       </c>
     </row>
@@ -6097,31 +6035,31 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.37%</t>
+        <v>0.03</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0394</v>
+        <v>0.0441</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0441</v>
       </c>
       <c r="K27" s="8" t="n">
         <v>0.0275</v>
@@ -6134,48 +6072,48 @@
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>2083/06/01 (Nepali notice)</t>
+          <t>2083/05/01 (Nepali notice)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Agricultural Development Bank Ltd.</t>
+          <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0275</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.0339</v>
+        <v>0.028</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0275</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0394</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.0428</v>
       </c>
       <c r="K28" s="8" t="n">
         <v>0.0275</v>
@@ -6188,7 +6126,7 @@
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
+          <t>2083/06/01 (Nepali notice)</t>
         </is>
       </c>
     </row>
@@ -6205,28 +6143,28 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.0278</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.0304</v>
+        <v>0.0339</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.0278</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.0278</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>0.0415</v>
@@ -6242,14 +6180,14 @@
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>Aswin 01, 2083 (17 Sep 2026)</t>
+          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Citizens Bank International Ltd.</t>
+          <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -6259,48 +6197,44 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0277</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0304</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0277</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0277</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0415</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083 (17 Aug 2026)</t>
+          <t>Aswin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -6317,11 +6251,11 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>0.0275</v>
@@ -6354,18 +6288,18 @@
         </is>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
-          <t>1 Ashwin 2083 (17 Sep 2026)</t>
+          <t>1st Bhadra 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Everest Bank Ltd.</t>
+          <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -6375,44 +6309,48 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.50%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0285</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.0405</v>
-      </c>
-      <c r="K32" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0385</v>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+          <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -6429,11 +6367,11 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>0.0275</v>
@@ -6453,7 +6391,7 @@
         <v>0.0275</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0405</v>
       </c>
       <c r="K33" s="8" t="n">
         <v>0.0275</v>
@@ -6462,18 +6400,18 @@
         <v>0.0275</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.035</v>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1 Ashoj 2083)</t>
+          <t>17 Aug 2026 (1st Bhadra 2083)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Global IME Bank Ltd.</t>
+          <t>Everest Bank Ltd.</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -6483,11 +6421,11 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="8" t="n">
         <v>0.0275</v>
@@ -6497,32 +6435,30 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.50%</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K34" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0375</v>
+      </c>
+      <c r="K34" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L34" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
+          <t>17 Sep 2026 (1 Ashoj 2083)</t>
         </is>
       </c>
     </row>
@@ -6539,11 +6475,11 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>0.0275</v>
@@ -6578,14 +6514,14 @@
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Himalayan Bank Ltd.</t>
+          <t>Global IME Bank Ltd.</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -6595,60 +6531,46 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+      <c r="L36" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083 (Nepali notice)</t>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -6665,67 +6587,51 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Shrawan 2083</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="M37" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>0.035</v>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>Shrawan 01, 2083 (17 Jul 2026)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Kumari Bank Ltd.</t>
+          <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -6745,41 +6651,41 @@
         <v>0.0275</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0325</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.81%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.04</v>
       </c>
       <c r="K38" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.035</v>
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>01 Bhadra 2083 (17 Aug 2026)</t>
+          <t>Bhadra 2083 (Nepali notice)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Kumari Bank Ltd.</t>
+          <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -6799,41 +6705,41 @@
         <v>0.0275</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0325</v>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.81%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>0.0343</v>
+        <v>0.04</v>
       </c>
       <c r="K39" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.035</v>
       </c>
       <c r="N39" s="10" t="inlineStr">
         <is>
-          <t>01 Ashwin 2083 (17 Sep 2026)</t>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank Ltd.</t>
+          <t>Kumari Bank Ltd.</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -6853,21 +6759,21 @@
         <v>0.0275</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0391</v>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.81%</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0346</v>
       </c>
       <c r="K40" s="8" t="n">
         <v>0.0275</v>
@@ -6876,18 +6782,18 @@
         <v>0.0275</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0301</v>
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>01 Bhadra 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank Ltd.</t>
+          <t>Kumari Bank Ltd.</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -6907,21 +6813,21 @@
         <v>0.0275</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0391</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.81%</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0343</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>0.0275</v>
@@ -6930,18 +6836,18 @@
         <v>0.0275</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0301</v>
       </c>
       <c r="N41" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026</t>
+          <t>01 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank Ltd.</t>
+          <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -6958,24 +6864,24 @@
         <v>2</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.028</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>0.03</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="K42" s="8" t="n">
         <v>0.0275</v>
@@ -6984,7 +6890,7 @@
         <v>0.0275</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0325</v>
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
@@ -6995,7 +6901,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank Ltd.</t>
+          <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -7019,17 +6925,17 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>0.03</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="K43" s="8" t="n">
         <v>0.0275</v>
@@ -7038,7 +6944,7 @@
         <v>0.0275</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0325</v>
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
@@ -7049,7 +6955,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>NIC Asia Bank Ltd.</t>
+          <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -7066,24 +6972,24 @@
         <v>2</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0301</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="K44" s="8" t="n">
         <v>0.0275</v>
@@ -7096,14 +7002,14 @@
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083 (17 Aug 2026)</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>NIC Asia Bank Ltd.</t>
+          <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -7123,21 +7029,21 @@
         <v>0.0275</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="K45" s="8" t="n">
         <v>0.0275</v>
@@ -7150,14 +7056,14 @@
       </c>
       <c r="N45" s="10" t="inlineStr">
         <is>
-          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+          <t>17 Sep 2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>NMB Bank Ltd.</t>
+          <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -7181,7 +7087,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
@@ -7191,7 +7097,7 @@
         <v>0.0275</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="K46" s="8" t="n">
         <v>0.0275</v>
@@ -7200,18 +7106,18 @@
         <v>0.0275</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="N46" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 1, 2083 (17 Aug 2026)</t>
+          <t>1st Bhadra 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>NMB Bank Ltd.</t>
+          <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -7235,7 +7141,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
@@ -7245,29 +7151,27 @@
         <v>0.0275</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K47" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="N47" s="10" t="inlineStr">
         <is>
-          <t>Asoj 1, 2083 (17 Sep 2026)</t>
+          <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Nabil Bank Ltd.</t>
+          <t>NMB Bank Ltd.</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -7287,7 +7191,7 @@
         <v>0.0275</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
@@ -7295,13 +7199,13 @@
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.045</v>
       </c>
       <c r="K48" s="8" t="n">
         <v>0.0275</v>
@@ -7310,18 +7214,18 @@
         <v>0.0275</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.035</v>
       </c>
       <c r="N48" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+          <t>Bhadra 1, 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Nabil Bank Ltd.</t>
+          <t>NMB Bank Ltd.</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -7341,7 +7245,7 @@
         <v>0.0275</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
@@ -7349,33 +7253,35 @@
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="K49" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.045</v>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L49" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.035</v>
       </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1 Ashwin 2083)</t>
+          <t>Asoj 1, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Nepal Bank Ltd.</t>
+          <t>Nabil Bank Ltd.</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -7395,21 +7301,21 @@
         <v>0.0275</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0285</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0285</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.0455</v>
       </c>
       <c r="K50" s="8" t="n">
         <v>0.0275</v>
@@ -7418,18 +7324,18 @@
         <v>0.0275</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0301</v>
       </c>
       <c r="N50" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083</t>
+          <t>17 Aug 2026 (1st Bhadra 2083)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Nepal Bank Ltd.</t>
+          <t>Nabil Bank Ltd.</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -7446,44 +7352,44 @@
         <v>3</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="F51" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M51" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="n">
-        <v>0.0276</v>
-      </c>
-      <c r="I51" s="8" t="n">
-        <v>0.0276</v>
-      </c>
-      <c r="J51" s="8" t="n">
-        <v>0.0415</v>
-      </c>
-      <c r="K51" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L51" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M51" s="8" t="n">
-        <v>0.035</v>
-      </c>
       <c r="N51" s="10" t="inlineStr">
         <is>
-          <t>1st Ashwin 2083</t>
+          <t>17 Sep 2026 (1 Ashwin 2083)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank Ltd.</t>
+          <t>Nepal Bank Ltd.</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -7503,26 +7409,24 @@
         <v>0.0275</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.03</v>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.35%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0276</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0276</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0415</v>
+      </c>
+      <c r="K52" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L52" s="8" t="n">
         <v>0.0275</v>
@@ -7532,14 +7436,14 @@
       </c>
       <c r="N52" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+          <t>1st Bhadra 2083</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank Ltd.</t>
+          <t>Nepal Bank Ltd.</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -7556,29 +7460,27 @@
         <v>3</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0301</v>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.35%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0276</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0276</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K53" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0415</v>
+      </c>
+      <c r="K53" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L53" s="8" t="n">
         <v>0.0275</v>
@@ -7588,14 +7490,14 @@
       </c>
       <c r="N53" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+          <t>1st Ashwin 2083</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank Ltd.</t>
+          <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -7615,30 +7517,32 @@
         <v>0.0275</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0375</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.75%</t>
+          <t>Up to 1.35%</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I54" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="I54" s="8" t="n">
-        <v>0.032</v>
-      </c>
       <c r="J54" s="8" t="n">
-        <v>0.04099999999999999</v>
-      </c>
-      <c r="K54" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.045</v>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L54" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="N54" s="10" t="inlineStr">
         <is>
@@ -7649,7 +7553,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank Ltd.</t>
+          <t>Nepal Investment Mega Bank Ltd.</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -7669,30 +7573,32 @@
         <v>0.0275</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0375</v>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.75%</t>
+          <t>Up to 1.35%</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I55" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="I55" s="8" t="n">
-        <v>0.032</v>
-      </c>
       <c r="J55" s="8" t="n">
-        <v>0.04099999999999999</v>
-      </c>
-      <c r="K55" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.045</v>
+      </c>
+      <c r="K55" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L55" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="N55" s="10" t="inlineStr">
         <is>
@@ -7703,7 +7609,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Prabhu Bank Ltd.</t>
+          <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -7723,21 +7629,21 @@
         <v>0.0275</v>
       </c>
       <c r="F56" s="8" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.75%</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.10%</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>0.0275</v>
-      </c>
       <c r="I56" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.032</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="K56" s="8" t="n">
         <v>0.0275</v>
@@ -7750,14 +7656,14 @@
       </c>
       <c r="N56" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (01 Bhadra 2083)</t>
+          <t>17 Aug 2026 (1st Bhadra 2083)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Prabhu Bank Ltd.</t>
+          <t>Nepal SBI Bank Ltd.</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -7777,21 +7683,21 @@
         <v>0.0275</v>
       </c>
       <c r="F57" s="8" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.75%</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.10%</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="n">
-        <v>0.0275</v>
-      </c>
       <c r="I57" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.032</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="K57" s="8" t="n">
         <v>0.0275</v>
@@ -7804,14 +7710,14 @@
       </c>
       <c r="N57" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (01 Ashwin 2083)</t>
+          <t>17 Sep 2026 (1st Ashwin 2083)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank Ltd.</t>
+          <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -7828,24 +7734,24 @@
         <v>2</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>0.0302</v>
+        <v>0.03</v>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 0.10%</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0455</v>
       </c>
       <c r="K58" s="8" t="n">
         <v>0.0275</v>
@@ -7858,14 +7764,14 @@
       </c>
       <c r="N58" s="10" t="inlineStr">
         <is>
-          <t>01st Bhadra 2083 (17 Aug 2026)</t>
+          <t>17 Aug 2026 (01 Bhadra 2083)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank Ltd.</t>
+          <t>Prabhu Bank Ltd.</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -7882,24 +7788,24 @@
         <v>3</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0.0302</v>
+        <v>0.03</v>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 0.10%</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0455</v>
       </c>
       <c r="K59" s="8" t="n">
         <v>0.0275</v>
@@ -7912,14 +7818,14 @@
       </c>
       <c r="N59" s="10" t="inlineStr">
         <is>
-          <t>01st Ashwin 2083 (17 Sep 2026)</t>
+          <t>17 Sep 2026 (01 Ashwin 2083)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank Ltd.</t>
+          <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -7936,21 +7842,21 @@
         <v>2</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0302</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I60" s="8" t="n">
         <v>0.03</v>
-      </c>
-      <c r="I60" s="8" t="n">
-        <v>0.0315</v>
       </c>
       <c r="J60" s="8" t="n">
         <v>0.04</v>
@@ -7962,18 +7868,18 @@
         <v>0.0275</v>
       </c>
       <c r="M60" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="N60" s="10" t="inlineStr">
         <is>
-          <t>2083 Bhadra 01 (17 Aug 2026)</t>
+          <t>01st Bhadra 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank Ltd.</t>
+          <t>Prime Commercial Bank Ltd.</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -7990,21 +7896,21 @@
         <v>3</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0302</v>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I61" s="8" t="n">
         <v>0.03</v>
-      </c>
-      <c r="I61" s="8" t="n">
-        <v>0.0315</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>0.04</v>
@@ -8016,18 +7922,18 @@
         <v>0.0275</v>
       </c>
       <c r="M61" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="N61" s="10" t="inlineStr">
         <is>
-          <t>2083 Asoj 01 (17 Sep 2026)</t>
+          <t>01st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Sanima Bank Ltd.</t>
+          <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -8051,17 +7957,17 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0315</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="K62" s="8" t="n">
         <v>0.0275</v>
@@ -8070,18 +7976,18 @@
         <v>0.0275</v>
       </c>
       <c r="M62" s="8" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="N62" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>2083 Bhadra 01 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Sanima Bank Ltd.</t>
+          <t>Rastriya Banijya Bank Ltd.</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -8105,17 +8011,17 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0315</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="K63" s="8" t="n">
         <v>0.0275</v>
@@ -8124,18 +8030,18 @@
         <v>0.0275</v>
       </c>
       <c r="M63" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.03</v>
       </c>
       <c r="N63" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 1, 2083</t>
+          <t>2083 Asoj 01 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Siddhartha Bank Ltd.</t>
+          <t>Sanima Bank Ltd.</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -8155,43 +8061,41 @@
         <v>0.0275</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.028</v>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>0.03759999999999999</v>
-      </c>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.045</v>
+      </c>
+      <c r="K64" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L64" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M64" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.033</v>
       </c>
       <c r="N64" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Siddhartha Bank Ltd.</t>
+          <t>Sanima Bank Ltd.</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -8211,43 +8115,41 @@
         <v>0.0275</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.028</v>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H65" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>0.03759999999999999</v>
-      </c>
-      <c r="K65" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.045</v>
+      </c>
+      <c r="K65" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L65" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M65" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.0351</v>
       </c>
       <c r="N65" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026</t>
+          <t>Ashwin 1, 2083</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal Ltd.</t>
+          <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -8267,7 +8169,7 @@
         <v>0.0275</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0305</v>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
@@ -8281,7 +8183,7 @@
         <v>0.0275</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>0.038</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="K66" s="11" t="inlineStr">
         <is>
@@ -8292,7 +8194,7 @@
         <v>0.0275</v>
       </c>
       <c r="M66" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0305</v>
       </c>
       <c r="N66" s="10" t="inlineStr">
         <is>
@@ -8303,7 +8205,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal Ltd.</t>
+          <t>Siddhartha Bank Ltd.</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -8323,41 +8225,153 @@
         <v>0.0275</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0305</v>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
+          <t>Up to 0.25%</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L67" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M67" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Ltd.</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.25%</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L68" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M68" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>17 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Ltd.</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
           <t>Up to 0.20%</t>
         </is>
       </c>
-      <c r="H67" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I67" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J67" s="8" t="n">
+      <c r="H69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J69" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="K67" s="11" t="inlineStr">
+      <c r="K69" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L67" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M67" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N67" s="10" t="inlineStr">
+      <c r="L69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N67"/>
+  <autoFilter ref="A1:N69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, SABBL, SADBL, SHINE.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, SABBL, SADBL, SHINE.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, NABBC, SABBL, SADBL, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, NABBC, SABBL, SADBL, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, NABBC, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, NABBC, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, NABBC, SABBL, SADBL, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, NABBC, SABBL, SADBL, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, NABBC, RBB, SABBL, SADBL, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: HBL, NABBC, RBB, SABBL, SADBL, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, HBL, NABBC, NBL, RBB, SABBL, SADBL, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, HBL, NABBC, NBL, RBB, SABBL, SADBL, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, HBL, MBL, NABBC, NBL, NMB, RBB, SABBL, SADBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, HBL, MBL, NABBC, NBL, NMB, RBB, SABBL, SADBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, GBIME, HBL, KSBBL, MBL, MNBBL, NABBC, NBL, NMB, RBB, SABBL, SADBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, GBIME, HBL, KSBBL, MBL, MNBBL, NABBC, NBL, NMB, RBB, SABBL, SADBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, GBIME, HBL, KSBBL, MBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, GBIME, HBL, KSBBL, MBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, GBIME, HBL, KSBBL, MBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: CORBL, GBIME, HBL, KSBBL, MBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, GBIME, HBL, KSBBL, MBL, MLBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, GBIME, HBL, KSBBL, MBL, MLBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, GBIME, HBL, KBL, KSBBL, MBL, MLBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, GBIME, HBL, KBL, KSBBL, MBL, MLBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, GBIME, GRDBL, HBL, KBL, KSBBL, LSL, MBL, MLBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, GBIME, GRDBL, HBL, KBL, KSBBL, LSL, MBL, MLBL, MNBBL, NABBC, NBL, NMB, PCBL, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBIME, GRDBL, HBL, KBL, KSBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NMB, PCBL, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBIME, GRDBL, HBL, KBL, KSBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NMB, PCBL, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBBL, GBIME, GRDBL, HBL, KBL, KSBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NMB, PCBL, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBBL, GBIME, GRDBL, HBL, KBL, KSBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NMB, PCBL, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBBL, GBIME, GRDBL, HBL, JBBL, KBL, KSBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NMB, PCBL, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBBL, GBIME, GRDBL, HBL, JBBL, KBL, KSBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NMB, PCBL, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBBL, GBIME, GRDBL, HBL, JBBL, KBL, KSBBL, LBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NMB, PCBL, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3492,7 +3492,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBBL, GBIME, GRDBL, HBL, JBBL, KBL, KSBBL, LBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NMB, PCBL, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBBL, GBIME, GRDBL, HBL, JBBL, KBL, KSBBL, LBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NIMB, NMB, PCBL, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Interest Rate Summary'!$A$4:$AB$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Development FD Spread'!$A$4:$V$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly History'!$A$1:$N$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly History'!$A$1:$N$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +585,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank Deposit Interest Rates — Ashwin 2083 vs Bhadra 2083</t>
+          <t>Bank Deposit Interest Rates — Kartik 2083 vs Ashwin 2083</t>
         </is>
       </c>
     </row>
@@ -643,14 +643,14 @@
       <c r="A4" s="3" t="n"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Min Kartik 2083</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>Min Ashwin 2083</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Min Bhadra 2083</t>
-        </is>
-      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Changes</t>
@@ -658,14 +658,14 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Max Kartik 2083</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>Max Ashwin 2083</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Max Bhadra 2083</t>
-        </is>
-      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Changes</t>
@@ -673,14 +673,14 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Ashwin 2083</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Bhadra 2083</t>
-        </is>
-      </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Changes</t>
@@ -688,14 +688,14 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>Less Than 1 Year Max Kartik 2083</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>Less Than 1 Year Max Ashwin 2083</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Less Than 1 Year Max Bhadra 2083</t>
-        </is>
-      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Less Than 1 Year Max Changes</t>
@@ -703,14 +703,14 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
+          <t>1 Year Kartik 2083</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
           <t>1 Year Ashwin 2083</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1 Year Bhadra 2083</t>
-        </is>
-      </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
           <t>1 Year Changes</t>
@@ -718,14 +718,14 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
+          <t>More Than 1 Year Max Kartik 2083</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
           <t>More Than 1 Year Max Ashwin 2083</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>More Than 1 Year Max Bhadra 2083</t>
-        </is>
-      </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
           <t>More Than 1 Year Max Changes</t>
@@ -733,14 +733,14 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
+          <t>Less Than 1 Year Max Kartik 2083</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>Less Than 1 Year Max Ashwin 2083</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>Less Than 1 Year Max Bhadra 2083</t>
-        </is>
-      </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Less Than 1 Year Max Changes</t>
@@ -748,14 +748,14 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
+          <t>1 Year Kartik 2083</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
           <t>1 Year Ashwin 2083</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1 Year Bhadra 2083</t>
-        </is>
-      </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>1 Year Changes</t>
@@ -763,12 +763,12 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
+          <t>More Than 1 Year Max Kartik 2083</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
           <t>More Than 1 Year Max Ashwin 2083</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>More Than 1 Year Max Bhadra 2083</t>
         </is>
       </c>
       <c r="AB4" s="4" t="inlineStr">
@@ -814,99 +814,99 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Garima Bikas Bank Ltd.</t>
+          <t>Garima Bikas Bank Limited</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0.0375</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
+          <t>Up to 1.38%</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
           <t>Up to 1.37%</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.37%</t>
-        </is>
-      </c>
       <c r="J6" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="Q6" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="R6" s="8" t="n">
         <v>0.0428</v>
-      </c>
-      <c r="R6" s="8" t="n">
-        <v>0.0441</v>
       </c>
       <c r="S6" s="9" t="n">
         <v>-0.0013</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="U6" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="X6" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="Z6" s="8" t="n">
         <v>0.0325</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Jyoti Bikas Bank Ltd.</t>
+          <t>Jyoti Bikash Bank Ltd.</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>0.0428</v>
-      </c>
-      <c r="R7" s="8" t="n">
-        <v>0.0441</v>
       </c>
       <c r="S7" s="9" t="n">
         <v>-0.0013</v>
@@ -1051,10 +1051,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="R8" s="8" t="n">
         <v>0.0428</v>
-      </c>
-      <c r="R8" s="8" t="n">
-        <v>0.0441</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>-0.0013</v>
@@ -1087,10 +1087,10 @@
         <v>0.0335</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0335</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1112,10 +1112,10 @@
         <v>0.028</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -1134,28 +1134,28 @@
         <v>0.028</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>0.028</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="8" t="n">
         <v>0.045</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="T9" s="11" t="inlineStr">
         <is>
@@ -1247,19 +1247,19 @@
         <v>0.028</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>0.043</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="T10" s="11" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
         <v>0.0425</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.0425</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1311,26 +1311,26 @@
         <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0277</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>0.028</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0</v>
+        <v>-0.0003</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
+          <t>Up to 0.10%</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
           <t>Up to 1.00%</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.00%</t>
-        </is>
-      </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0.0275</v>
@@ -1351,10 +1351,10 @@
         <v>0</v>
       </c>
       <c r="Q11" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="R11" s="8" t="n">
         <v>0.0428</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>0.0441</v>
       </c>
       <c r="S11" s="9" t="n">
         <v>-0.0013</v>
@@ -1364,8 +1364,10 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v>0.0275</v>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="V11" s="11" t="inlineStr">
         <is>
@@ -1382,10 +1384,10 @@
         <v>0</v>
       </c>
       <c r="Z11" s="8" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="AA11" s="8" t="n">
         <v>0.032</v>
-      </c>
-      <c r="AA11" s="8" t="n">
-        <v>0.0325</v>
       </c>
       <c r="AB11" s="9" t="n">
         <v>-0.0005</v>
@@ -1450,10 +1452,10 @@
         <v>0.0428</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.0428</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>-0.0013</v>
+        <v>0</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>0.0275</v>
@@ -1499,13 +1501,13 @@
         <v>0</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.03</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>0.0325</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0</v>
+        <v>-0.0025</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -1539,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0415</v>
       </c>
       <c r="R13" s="8" t="n">
         <v>0.0459</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0</v>
+        <v>-0.0044</v>
       </c>
       <c r="T13" s="8" t="n">
         <v>0.0275</v>
@@ -1566,13 +1568,13 @@
         <v>0</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0315</v>
       </c>
       <c r="AA13" s="8" t="n">
         <v>0.035</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>0</v>
+        <v>-0.0035</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1616,22 +1618,22 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <v>0.0278</v>
-      </c>
       <c r="D15" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="E15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>0.0304</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>0.0339</v>
-      </c>
       <c r="G15" s="9" t="n">
-        <v>-0.0035</v>
+        <v>-0.0029</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
@@ -1640,29 +1642,29 @@
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>-0.0015</v>
+        <v>0</v>
       </c>
       <c r="K15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L15" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="L15" s="8" t="n">
-        <v>0.0278</v>
-      </c>
       <c r="M15" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="N15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O15" s="8" t="n">
         <v>0.0277</v>
       </c>
-      <c r="O15" s="8" t="n">
-        <v>0.0278</v>
-      </c>
       <c r="P15" s="9" t="n">
-        <v>-0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="Q15" s="8" t="n">
         <v>0.0415</v>
@@ -1704,7 +1706,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Citizens Bank International Ltd.</t>
+          <t>Citizens Bank International Limited</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -1799,16 +1801,16 @@
         <v>0.0275</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Everest Bank Ltd.</t>
+          <t>Everest Bank Limited</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -1831,7 +1833,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.50%</t>
+          <t>Upto 0.50%</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -1864,10 +1866,10 @@
         <v>0.0375</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.0375</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="T17" s="8" t="n">
         <v>0.0275</v>
@@ -1891,16 +1893,16 @@
         <v>0.0325</v>
       </c>
       <c r="AA17" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="AB17" s="9" t="n">
-        <v>-0.0025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Global IME Bank Ltd.</t>
+          <t>Global IME Bank Limited</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
@@ -1998,7 +2000,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Himalayan Bank Ltd.</t>
+          <t>Himalayan Bank Limited</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -2078,38 +2080,38 @@
         <v>0</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="AA19" s="8" t="n">
         <v>0.035</v>
       </c>
       <c r="AB19" s="9" t="n">
-        <v>0</v>
+        <v>-0.0025</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Kumari Bank Ltd.</t>
+          <t>Kumari Bank Limited</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.0392</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>0.0391</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
@@ -2143,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="Q20" s="8" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>0.0343</v>
-      </c>
-      <c r="R20" s="8" t="n">
-        <v>0.0346</v>
       </c>
       <c r="S20" s="9" t="n">
         <v>-0.0003</v>
@@ -2170,19 +2172,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="AA20" s="8" t="n">
         <v>0.0301</v>
       </c>
       <c r="AB20" s="9" t="n">
-        <v>0</v>
+        <v>-0.0026</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank Ltd.</t>
+          <t>Laxmi Sunrise Bank Limited</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -2274,26 +2276,26 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank Ltd.</t>
+          <t>Machhapuchchhre Bank Limited</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>-0.0001</v>
+        <v>0</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>0.028</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.028</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>-0.0021</v>
+        <v>0</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
@@ -2366,7 +2368,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Nabil Bank Ltd.</t>
+          <t>Nabil Bank Limited</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -2401,31 +2403,31 @@
         <v>0</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.028</v>
       </c>
       <c r="L23" s="8" t="n">
         <v>0.0285</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.028</v>
       </c>
       <c r="O23" s="8" t="n">
         <v>0.0285</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="Q23" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="R23" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="R23" s="8" t="n">
-        <v>0.0455</v>
-      </c>
       <c r="S23" s="9" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="T23" s="8" t="n">
         <v>0.0275</v>
@@ -2446,38 +2448,38 @@
         <v>0</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="AA23" s="8" t="n">
         <v>0.0301</v>
       </c>
       <c r="AB23" s="9" t="n">
-        <v>0</v>
+        <v>-0.0026</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Nepal Bank Ltd.</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="C24" s="8" t="n">
         <v>0.0276</v>
       </c>
-      <c r="C24" s="8" t="n">
-        <v>0.0275</v>
-      </c>
       <c r="D24" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0001</v>
       </c>
       <c r="E24" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F24" s="8" t="n">
         <v>0.0301</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>0.03</v>
-      </c>
       <c r="G24" s="9" t="n">
-        <v>0.0001</v>
+        <v>-0.0026</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
@@ -2486,11 +2488,11 @@
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="K24" s="8" t="n">
         <v>0.0276</v>
@@ -2550,7 +2552,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>NIC Asia Bank Ltd.</t>
+          <t>NIC Asia Bank Limited</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -2646,22 +2648,22 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>0.0375</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
@@ -2676,14 +2678,18 @@
       <c r="J26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="8" t="n">
-        <v>0.029</v>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L26" s="8" t="n">
         <v>0.029</v>
       </c>
-      <c r="M26" s="9" t="n">
-        <v>0</v>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N26" s="8" t="n">
         <v>0.03</v>
@@ -2695,13 +2701,13 @@
         <v>0</v>
       </c>
       <c r="Q26" s="8" t="n">
-        <v>0.045</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="R26" s="8" t="n">
         <v>0.045</v>
       </c>
       <c r="S26" s="9" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="T26" s="11" t="inlineStr">
         <is>
@@ -2728,19 +2734,19 @@
         <v>0</v>
       </c>
       <c r="Z26" s="8" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="AA26" s="8" t="n">
         <v>0.035</v>
       </c>
       <c r="AB26" s="9" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>NMB Bank Ltd.</t>
+          <t>NMB Bank Limited</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
@@ -2806,8 +2812,10 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v>0.0275</v>
+      <c r="U27" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="V27" s="11" t="inlineStr">
         <is>
@@ -2928,7 +2936,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Prabhu Bank Ltd.</t>
+          <t>Prabhu Bank Limited</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -2981,13 +2989,13 @@
         <v>0</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0425</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>0.0455</v>
       </c>
       <c r="S29" s="9" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="T29" s="8" t="n">
         <v>0.0275</v>
@@ -3020,7 +3028,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank Ltd.</t>
+          <t>Rastriya Banijya Bank Limited</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
@@ -3112,7 +3120,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Sanima Bank Ltd.</t>
+          <t>Sanima Bank Limited</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -3195,10 +3203,10 @@
         <v>0.0351</v>
       </c>
       <c r="AA31" s="8" t="n">
-        <v>0.033</v>
+        <v>0.0351</v>
       </c>
       <c r="AB31" s="9" t="n">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -3227,16 +3235,16 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
+          <t>Up to 0.35%</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
           <t>Up to 0.75%</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.75%</t>
-        </is>
-      </c>
       <c r="J32" s="9" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="K32" s="8" t="n">
         <v>0.03</v>
@@ -3257,13 +3265,13 @@
         <v>0</v>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="R32" s="8" t="n">
         <v>0.04099999999999999</v>
       </c>
       <c r="S32" s="9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="T32" s="8" t="n">
         <v>0.0275</v>
@@ -3296,7 +3304,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Siddhartha Bank Ltd.</t>
+          <t>Siddhartha Bank Limited</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -3319,7 +3327,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>up to 0.25%</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -3394,7 +3402,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal Ltd.</t>
+          <t>Standard Chartered Bank Nepal Limited</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
@@ -3417,12 +3425,12 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
+          <t>Up to 0.15%</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
           <t>Up to 0.20%</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
@@ -3447,10 +3455,10 @@
         <v>0</v>
       </c>
       <c r="Q34" s="8" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>0.0375</v>
-      </c>
-      <c r="R34" s="8" t="n">
-        <v>0.038</v>
       </c>
       <c r="S34" s="9" t="n">
         <v>-0.0005</v>
@@ -3492,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: ADBL, CORBL, CZBIL, EBL, GBBL, GBIME, GRDBL, HBL, JBBL, KBL, KSBBL, LBBL, LSL, MBL, MLBL, MNBBL, NABBC, NABIL, NBL, NICA, NIMB, NMB, PCBL, PRVU, RBB, SABBL, SADBL, SANIMA, SBI, SBL, SCB, SHINE, SINDU.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3682,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Development Banks — Fixed Deposit: Individual vs Institutional (Ashwin 2083)</t>
+          <t>Development Banks — Fixed Deposit: Individual vs Institutional (Kartik 2083)</t>
         </is>
       </c>
     </row>
@@ -3845,11 +3853,11 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Garima Bikas Bank Ltd.</t>
+          <t>Garima Bikas Bank Limited</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
@@ -3862,19 +3870,19 @@
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>0</v>
@@ -3883,43 +3891,43 @@
         <v>0.03</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>0.0025</v>
+        <v>0.0024</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>0.03</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>0.005</v>
+        <v>0.0025</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="R5" s="8" t="n">
         <v>0.03</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>0.005</v>
+        <v>0.0025</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0415</v>
       </c>
       <c r="U5" s="8" t="n">
         <v>0.0325</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0.0103</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Jyoti Bikas Bank Ltd.</t>
+          <t>Jyoti Bikash Bank Ltd.</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -3981,13 +3989,13 @@
         <v>0</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0415</v>
       </c>
       <c r="U6" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0.0153</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -4059,13 +4067,13 @@
         <v>-0.002</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0415</v>
       </c>
       <c r="U7" s="8" t="n">
         <v>0.0335</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -4297,13 +4305,13 @@
         <v>0.005</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0415</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>0.032</v>
+        <v>0.0315</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0.0108</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -4441,19 +4449,19 @@
         <v>0.0375</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.03</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0.005</v>
+        <v>0.0075</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>0.0459</v>
+        <v>0.0415</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0315</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0.0109</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="14">
@@ -4563,7 +4571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4657,7 +4665,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Corporate Development Bank Ltd.</t>
+          <t>Corporate Development Bank Limited</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -4667,44 +4675,46 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0285</v>
       </c>
       <c r="F2" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.42%</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="I2" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.50%</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>0.045</v>
-      </c>
       <c r="J2" s="8" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0.03</v>
+        <v>0.055</v>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0475</v>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>1 Bhadra 2083 (17 Aug 2026)</t>
+          <t>01 Kartik, 2083 (18th October, 2026)</t>
         </is>
       </c>
     </row>
@@ -4721,51 +4731,51 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.03</v>
       </c>
       <c r="F3" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.50%</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.42%</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>0.0375</v>
-      </c>
       <c r="I3" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.045</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0.055</v>
+        <v>0.0575</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.03</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.035</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0.0475</v>
+        <v>0.05</v>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>1 Ashwin 2083 (17 Sep 2026)</t>
+          <t>1 Bhadra 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Garima Bikas Bank Ltd.</t>
+          <t>Corporate Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -4775,51 +4785,51 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0285</v>
       </c>
       <c r="F4" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.42%</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.37%</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>0.0275</v>
-      </c>
       <c r="I4" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0425</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.055</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0285</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0475</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>2083.05.01 (17 Aug 2026)</t>
+          <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Garima Bikas Bank Ltd.</t>
+          <t>Garima Bikas Bank Limited</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -4829,51 +4839,51 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.38%</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0415</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="M5" s="8" t="n">
         <v>0.0325</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>2083.06.01 (17 Sep 2026)</t>
+          <t>2083.07.01 (October 18, 2026)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Green Development Bank Ltd.</t>
+          <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -4893,41 +4903,41 @@
         <v>0.0275</v>
       </c>
       <c r="F6" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M6" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>0.0555</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>0.0455</v>
-      </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083</t>
+          <t>2083.05.01 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Green Development Bank Ltd.</t>
+          <t>Garima Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -4947,41 +4957,41 @@
         <v>0.0275</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0375</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0275</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.0525</v>
+        <v>0.0428</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0325</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>1st Ashoj 2083</t>
+          <t>2083.06.01 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Jyoti Bikas Bank Ltd.</t>
+          <t>Green Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -5001,7 +5011,7 @@
         <v>0.0275</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -5009,33 +5019,33 @@
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.04</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.0555</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0455</v>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
+          <t>1st Bhadra 2083</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Jyoti Bikas Bank Ltd.</t>
+          <t>Green Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -5055,7 +5065,7 @@
         <v>0.0275</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -5063,33 +5073,33 @@
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.04</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0525</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0425</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>1st Ashoj 2083</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Kamana Sewa Bikas Bank Ltd.</t>
+          <t>Green Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -5099,53 +5109,51 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F10" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>0.0441</v>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>0.0275</v>
-      </c>
       <c r="M10" s="8" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083 (17 Aug 2026)</t>
+          <t>1st Kartik 2083</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Kamana Sewa Bikas Bank Ltd.</t>
+          <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -5155,17 +5163,17 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -5179,29 +5187,27 @@
         <v>0.0275</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.0428</v>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0441</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0275</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Lumbini Bikas Bank Ltd.</t>
+          <t>Jyoti Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -5211,53 +5217,51 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0428</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L12" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>Bhadra month 2083</t>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Lumbini Bikas Bank Ltd.</t>
+          <t>Jyoti Bikash Bank Ltd.</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -5267,53 +5271,51 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0415</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>Ashwin month 2083</t>
+          <t>Kartik 01, 2083 (October 18, 2026)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Mahalaxmi Bikas Bank Ltd.</t>
+          <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -5333,45 +5335,43 @@
         <v>0.0275</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I14" s="8" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="L14" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0.0445</v>
+        <v>0.035</v>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+          <t>1st Bhadra 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Mahalaxmi Bikas Bank Ltd.</t>
+          <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5391,45 +5391,43 @@
         <v>0.0275</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Up to 1.375%</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="L15" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0335</v>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1st Aswin 2083)</t>
+          <t>1st Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Muktinath Bikas Bank Ltd.</t>
+          <t>Kamana Sewa Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -5439,21 +5437,21 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.00%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
@@ -5463,27 +5461,29 @@
         <v>0.0275</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.0441</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0415</v>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L16" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0335</v>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083</t>
+          <t>1st Kartik 2083 (18 Oct 2026)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Muktinath Bikas Bank Ltd.</t>
+          <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -5493,31 +5493,31 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.00%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.046</v>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
@@ -5528,18 +5528,18 @@
         <v>0.0275</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>1st Ashoj 2083</t>
+          <t>Bhadra month 2083</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Narayani Development Bank Ltd.</t>
+          <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -5549,51 +5549,53 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0.052</v>
+        <v>0.028</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>0.052</v>
+        <v>0.045</v>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.0275</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 1st 2083 (17 Aug 2026)</t>
+          <t>Ashwin month 2083</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Narayani Development Bank Ltd.</t>
+          <t>Lumbini Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -5603,51 +5605,53 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0495</v>
+        <v>0.028</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0515</v>
+        <v>0.028</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0.0495</v>
+        <v>0.045</v>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L19" s="8" t="n">
-        <v>0.0515</v>
+        <v>0.0275</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.0515</v>
+        <v>0.03</v>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Salapa Bikas Bank Ltd.</t>
+          <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -5667,41 +5671,45 @@
         <v>0.0275</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="J20" s="8" t="n">
         <v>0.045</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>0.04</v>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.0425</v>
+        <v>0.0275</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.05</v>
+        <v>0.0445</v>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083</t>
+          <t>17 Aug 2026 (1st Bhadra 2083)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Salapa Bikas Bank Ltd.</t>
+          <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -5721,41 +5729,45 @@
         <v>0.0275</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>0.045</v>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.05</v>
+        <v>0.028</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>0.04</v>
+        <v>0.043</v>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L21" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M21" s="8" t="n">
         <v>0.0425</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>0.05</v>
-      </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>Ashoj 01, 2083</t>
+          <t>17 Sep 2026 (1st Aswin 2083)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Shangri-la Development Bank Ltd.</t>
+          <t>Mahalaxmi Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -5765,11 +5777,11 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>0.0275</v>
@@ -5779,37 +5791,41 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>0.0275</v>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>0.0441</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.043</v>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L22" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0425</v>
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
+          <t>October 18, 2026 (1st Kartik, 2083)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Shangri-la Development Bank Ltd.</t>
+          <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -5819,21 +5835,21 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.00%</t>
         </is>
       </c>
       <c r="H23" s="8" t="n">
@@ -5843,7 +5859,7 @@
         <v>0.0275</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0441</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>0.0275</v>
@@ -5852,18 +5868,18 @@
         <v>0.0275</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>1st Bhadra 2083</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Shine Resunga Development Bank Ltd.</t>
+          <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -5873,51 +5889,53 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.028</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.00%</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0275</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="K24" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0428</v>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L24" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.035</v>
+        <v>0.032</v>
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>2083-05-01 (17 Aug 2026)</t>
+          <t>1st Ashoj 2083</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Shine Resunga Development Bank Ltd.</t>
+          <t>Muktinath Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -5927,51 +5945,53 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0277</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 0.10%</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0275</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0.0459</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0415</v>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L25" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0315</v>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>2083-06-01 (17 Sep 2026)</t>
+          <t>1st Kartik 2083</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Sindhu Bikash Bank Ltd.</t>
+          <t>Narayani Development Bank Limited</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -5981,51 +6001,51 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Shrawan 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
+        <v>0.0275</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>1.375%</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0495</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.046</v>
+        <v>0.0515</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>0.046</v>
+        <v>0.0515</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0495</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0515</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0515</v>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>2083/04/01 (Nepali notice)</t>
+          <t>Kartik 1st 2083 (October 18th 2026)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Sindhu Bikash Bank Ltd.</t>
+          <t>Narayani Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -6045,41 +6065,41 @@
         <v>0.0275</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
+        <v>0.0275</v>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>1.375%</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.052</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0.0441</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.052</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>2083/05/01 (Nepali notice)</t>
+          <t>Bhadra 1st 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Sindhu Bikash Bank Ltd.</t>
+          <t>Narayani Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -6099,279 +6119,271 @@
         <v>0.0275</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>1.375%</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0495</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.0394</v>
+        <v>0.0515</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0515</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0495</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0515</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0515</v>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>2083/06/01 (Nepali notice)</t>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Agricultural Development Bank Ltd.</t>
+          <t>Salapa Bikas Bank Limited</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.0275</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.0339</v>
+        <v>0.03</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>Upto 1.37%</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.045</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.05</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.055</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.04</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0425</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.05</v>
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
+          <t>1st Kartik, 2083</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Agricultural Development Bank Ltd.</t>
+          <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.0275</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.0304</v>
+        <v>0.03</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.045</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.05</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.0415</v>
+        <v>0.055</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.04</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0425</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.05</v>
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
-          <t>Aswin 01, 2083 (17 Sep 2026)</t>
+          <t>1st Bhadra 2083</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Citizens Bank International Ltd.</t>
+          <t>Salapa Bikas Bank Ltd.</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.045</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.029</v>
+        <v>0.05</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="K31" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.055</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>0.0425</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083 (17 Aug 2026)</t>
+          <t>Ashoj 01, 2083</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Citizens Bank International Ltd.</t>
+          <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0441</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="M32" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>1 Ashwin 2083 (17 Sep 2026)</t>
+          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Everest Bank Ltd.</t>
+          <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>0.0275</v>
@@ -6381,7 +6393,7 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.50%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
@@ -6391,7 +6403,7 @@
         <v>0.0275</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.0405</v>
+        <v>0.0428</v>
       </c>
       <c r="K33" s="8" t="n">
         <v>0.0275</v>
@@ -6400,32 +6412,32 @@
         <v>0.0275</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Everest Bank Ltd.</t>
+          <t>Shangri-la Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="8" t="n">
         <v>0.0275</v>
@@ -6435,7 +6447,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.50%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
@@ -6445,7 +6457,7 @@
         <v>0.0275</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0428</v>
       </c>
       <c r="K34" s="8" t="n">
         <v>0.0275</v>
@@ -6454,23 +6466,23 @@
         <v>0.0275</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0275</v>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1 Ashoj 2083)</t>
+          <t>Kartik 01, 2083 (October 18, 2026)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Global IME Bank Ltd.</t>
+          <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -6485,48 +6497,46 @@
         <v>0.0275</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0325</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K35" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0459</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
+          <t>2083-05-01 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Global IME Bank Ltd.</t>
+          <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -6541,239 +6551,237 @@
         <v>0.0275</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0325</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K36" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0459</v>
+      </c>
+      <c r="K36" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L36" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>2083-06-01 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Himalayan Bank Ltd.</t>
+          <t>Shine Resunga Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Shrawan 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E37" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F37" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I37" s="8" t="n">
         <v>0.0325</v>
       </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>0.03</v>
-      </c>
       <c r="J37" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0415</v>
       </c>
       <c r="K37" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0315</v>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>Shrawan 01, 2083 (17 Jul 2026)</t>
+          <t>2083-07-01 (18th October, 2026)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Himalayan Bank Ltd.</t>
+          <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Shrawan 2083</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0285</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
+        <v>0.03</v>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0276</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.03</v>
+        <v>0.046</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>0.04</v>
+        <v>0.046</v>
       </c>
       <c r="K38" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="M38" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083 (Nepali notice)</t>
+          <t>2083/04/01 (Nepali notice)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Himalayan Bank Ltd.</t>
+          <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>Up to 1.375%</t>
+        <v>0.03</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0276</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0441</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0441</v>
       </c>
       <c r="K39" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="N39" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
+          <t>2083/05/01 (Nepali notice)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Kumari Bank Ltd.</t>
+          <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.028</v>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.81%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0394</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.0346</v>
+        <v>0.0428</v>
       </c>
       <c r="K40" s="8" t="n">
         <v>0.0275</v>
@@ -6782,52 +6790,52 @@
         <v>0.0275</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>01 Bhadra 2083 (17 Aug 2026)</t>
+          <t>2083/06/01 (Nepali notice)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Kumari Bank Ltd.</t>
+          <t>Sindhu Bikash Bank Ltd.</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Commercial Banks</t>
+          <t>Development Banks</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.028</v>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.81%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0348</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>0.0343</v>
+        <v>0.0415</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>0.0275</v>
@@ -6836,18 +6844,18 @@
         <v>0.0275</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="N41" s="10" t="inlineStr">
         <is>
-          <t>01 Ashwin 2083 (17 Sep 2026)</t>
+          <t>2083/07/01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank Ltd.</t>
+          <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -6864,24 +6872,24 @@
         <v>2</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0278</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0339</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0278</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0278</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0415</v>
       </c>
       <c r="K42" s="8" t="n">
         <v>0.0275</v>
@@ -6890,18 +6898,18 @@
         <v>0.0275</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0275</v>
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank Ltd.</t>
+          <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -6918,24 +6926,24 @@
         <v>3</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0277</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0304</v>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0277</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0277</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0415</v>
       </c>
       <c r="K43" s="8" t="n">
         <v>0.0275</v>
@@ -6944,18 +6952,18 @@
         <v>0.0275</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0.0325</v>
+        <v>0.0275</v>
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026</t>
+          <t>Aswin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank Ltd.</t>
+          <t>Agricultural Development Bank Ltd.</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -6965,31 +6973,31 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0415</v>
       </c>
       <c r="K44" s="8" t="n">
         <v>0.0275</v>
@@ -6998,18 +7006,18 @@
         <v>0.0275</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>Kartik 01, 2083 (18 October, 2026)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank Ltd.</t>
+          <t>Citizens Bank International Limited</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -7019,11 +7027,11 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>0.0275</v>
@@ -7033,37 +7041,41 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0285</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K45" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L45" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0385</v>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="N45" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026</t>
+          <t>1st Kartik 2083 (18th October 2026)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>NIC Asia Bank Ltd.</t>
+          <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -7083,27 +7095,31 @@
         <v>0.0275</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0285</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0385</v>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="M46" s="8" t="n">
         <v>0.03</v>
@@ -7117,7 +7133,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>NIC Asia Bank Ltd.</t>
+          <t>Citizens Bank International Ltd.</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -7137,41 +7153,45 @@
         <v>0.0275</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0285</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.029</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K47" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="L47" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0385</v>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="N47" s="10" t="inlineStr">
         <is>
-          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+          <t>1 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>NMB Bank Ltd.</t>
+          <t>Everest Bank Limited</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -7181,11 +7201,11 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" s="8" t="n">
         <v>0.0275</v>
@@ -7195,7 +7215,7 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Upto 0.50%</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -7205,7 +7225,7 @@
         <v>0.0275</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.045</v>
+        <v>0.0375</v>
       </c>
       <c r="K48" s="8" t="n">
         <v>0.0275</v>
@@ -7214,18 +7234,18 @@
         <v>0.0275</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="N48" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 1, 2083 (17 Aug 2026)</t>
+          <t>18th October 2026 (1st Kartik 2083)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>NMB Bank Ltd.</t>
+          <t>Everest Bank Ltd.</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -7235,11 +7255,11 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>0.0275</v>
@@ -7249,7 +7269,7 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.50%</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
@@ -7259,12 +7279,10 @@
         <v>0.0275</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K49" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.0405</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L49" s="8" t="n">
         <v>0.0275</v>
@@ -7274,14 +7292,14 @@
       </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>Asoj 1, 2083 (17 Sep 2026)</t>
+          <t>17 Aug 2026 (1st Bhadra 2083)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Nabil Bank Ltd.</t>
+          <t>Everest Bank Ltd.</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -7291,31 +7309,31 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.50%</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0275</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0375</v>
       </c>
       <c r="K50" s="8" t="n">
         <v>0.0275</v>
@@ -7324,18 +7342,18 @@
         <v>0.0275</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0325</v>
       </c>
       <c r="N50" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+          <t>17 Sep 2026 (1 Ashoj 2083)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Nabil Bank Ltd.</t>
+          <t>Global IME Bank Limited</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -7345,17 +7363,17 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0275</v>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
@@ -7363,33 +7381,35 @@
         </is>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0276</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0285</v>
+        <v>0.0276</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="K51" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.04</v>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L51" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="N51" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1 Ashwin 2083)</t>
+          <t>Kartik 01, 2083 (Oct 18, 2026)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Nepal Bank Ltd.</t>
+          <t>Global IME Bank Ltd.</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -7409,11 +7429,11 @@
         <v>0.0275</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
@@ -7423,27 +7443,29 @@
         <v>0.0276</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.0415</v>
-      </c>
-      <c r="K52" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.04</v>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L52" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="N52" s="10" t="inlineStr">
         <is>
-          <t>1st Bhadra 2083</t>
+          <t>Bhadra 01, 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Nepal Bank Ltd.</t>
+          <t>Global IME Bank Ltd.</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -7460,14 +7482,14 @@
         <v>3</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.0301</v>
+        <v>0.0275</v>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
@@ -7477,27 +7499,29 @@
         <v>0.0276</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>0.0415</v>
-      </c>
-      <c r="K53" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.04</v>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
       </c>
       <c r="L53" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0275</v>
       </c>
       <c r="N53" s="10" t="inlineStr">
         <is>
-          <t>1st Ashwin 2083</t>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank Ltd.</t>
+          <t>Himalayan Bank Limited</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -7507,21 +7531,21 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0325</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.35%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
@@ -7531,29 +7555,27 @@
         <v>0.03</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="K54" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
       <c r="N54" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+          <t>Kartik 01, 2083 (October18, 2026)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank Ltd.</t>
+          <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -7563,21 +7585,21 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Shrawan 2083</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E55" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.0375</v>
+        <v>0.0325</v>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.35%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
@@ -7587,29 +7609,27 @@
         <v>0.03</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K55" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="K55" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="M55" s="8" t="n">
         <v>0.035</v>
       </c>
       <c r="N55" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+          <t>Shrawan 01, 2083 (17 Jul 2026)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank Ltd.</t>
+          <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -7629,41 +7649,41 @@
         <v>0.0275</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0325</v>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.75%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I56" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="I56" s="8" t="n">
-        <v>0.032</v>
-      </c>
       <c r="J56" s="8" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="K56" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="N56" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+          <t>Bhadra 2083 (Nepali notice)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank Ltd.</t>
+          <t>Himalayan Bank Ltd.</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -7683,41 +7703,41 @@
         <v>0.0275</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.0279</v>
+        <v>0.0325</v>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.75%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I57" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="I57" s="8" t="n">
-        <v>0.032</v>
-      </c>
       <c r="J57" s="8" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="K57" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="M57" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.035</v>
       </c>
       <c r="N57" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+          <t>Ashwin 01, 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Prabhu Bank Ltd.</t>
+          <t>Kumari Bank Limited</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -7727,21 +7747,21 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0392</v>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.10%</t>
+          <t>Up to 0.81%</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
@@ -7751,7 +7771,7 @@
         <v>0.0275</v>
       </c>
       <c r="J58" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.034</v>
       </c>
       <c r="K58" s="8" t="n">
         <v>0.0275</v>
@@ -7764,14 +7784,14 @@
       </c>
       <c r="N58" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026 (01 Bhadra 2083)</t>
+          <t>01 Kartik 2083 (18 October 2026)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Prabhu Bank Ltd.</t>
+          <t>Kumari Bank Ltd.</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -7781,21 +7801,21 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0391</v>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.10%</t>
+          <t>Up to 0.81%</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
@@ -7805,7 +7825,7 @@
         <v>0.0275</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>0.0455</v>
+        <v>0.0346</v>
       </c>
       <c r="K59" s="8" t="n">
         <v>0.0275</v>
@@ -7814,18 +7834,18 @@
         <v>0.0275</v>
       </c>
       <c r="M59" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0301</v>
       </c>
       <c r="N59" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026 (01 Ashwin 2083)</t>
+          <t>01 Bhadra 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank Ltd.</t>
+          <t>Kumari Bank Ltd.</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -7835,31 +7855,31 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>0.0302</v>
+        <v>0.0391</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 0.81%</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0275</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0275</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>0.04</v>
+        <v>0.0343</v>
       </c>
       <c r="K60" s="8" t="n">
         <v>0.0275</v>
@@ -7868,18 +7888,18 @@
         <v>0.0275</v>
       </c>
       <c r="M60" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0301</v>
       </c>
       <c r="N60" s="10" t="inlineStr">
         <is>
-          <t>01st Bhadra 2083 (17 Aug 2026)</t>
+          <t>01 Ashwin 2083 (17 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank Ltd.</t>
+          <t>Laxmi Sunrise Bank Limited</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -7889,21 +7909,21 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.0276</v>
+        <v>0.0275</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.0302</v>
+        <v>0.028</v>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.37%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
@@ -7922,18 +7942,18 @@
         <v>0.0275</v>
       </c>
       <c r="M61" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="N61" s="10" t="inlineStr">
         <is>
-          <t>01st Ashwin 2083 (17 Sep 2026)</t>
+          <t>18th October, 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank Ltd.</t>
+          <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -7957,14 +7977,14 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I62" s="8" t="n">
         <v>0.03</v>
-      </c>
-      <c r="I62" s="8" t="n">
-        <v>0.0315</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>0.04</v>
@@ -7976,18 +7996,18 @@
         <v>0.0275</v>
       </c>
       <c r="M62" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0325</v>
       </c>
       <c r="N62" s="10" t="inlineStr">
         <is>
-          <t>2083 Bhadra 01 (17 Aug 2026)</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank Ltd.</t>
+          <t>Laxmi Sunrise Bank Ltd.</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -8011,14 +8031,14 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>Up to 1.375%</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I63" s="8" t="n">
         <v>0.03</v>
-      </c>
-      <c r="I63" s="8" t="n">
-        <v>0.0315</v>
       </c>
       <c r="J63" s="8" t="n">
         <v>0.04</v>
@@ -8030,18 +8050,18 @@
         <v>0.0275</v>
       </c>
       <c r="M63" s="8" t="n">
-        <v>0.03</v>
+        <v>0.0325</v>
       </c>
       <c r="N63" s="10" t="inlineStr">
         <is>
-          <t>2083 Asoj 01 (17 Sep 2026)</t>
+          <t>17 Sep 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Sanima Bank Ltd.</t>
+          <t>Machhapuchchhre Bank Limited</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -8051,11 +8071,11 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64" s="8" t="n">
         <v>0.0275</v>
@@ -8065,14 +8085,14 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>0.045</v>
@@ -8084,18 +8104,18 @@
         <v>0.0275</v>
       </c>
       <c r="M64" s="8" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="N64" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>18 October, 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Sanima Bank Ltd.</t>
+          <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -8105,28 +8125,28 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Bhadra 2083</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.0276</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>0.028</v>
+        <v>0.0301</v>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>Up to 1.375%</t>
+          <t>Up to 0.25%</t>
         </is>
       </c>
       <c r="H65" s="8" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="J65" s="8" t="n">
         <v>0.045</v>
@@ -8138,18 +8158,18 @@
         <v>0.0275</v>
       </c>
       <c r="M65" s="8" t="n">
-        <v>0.0351</v>
+        <v>0.03</v>
       </c>
       <c r="N65" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 1, 2083</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Siddhartha Bank Ltd.</t>
+          <t>Machhapuchchhre Bank Ltd.</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -8159,17 +8179,17 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Bhadra 2083</t>
+          <t>Ashwin 2083</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.028</v>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
@@ -8177,35 +8197,33 @@
         </is>
       </c>
       <c r="H66" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>0.03759999999999999</v>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.045</v>
+      </c>
+      <c r="K66" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L66" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M66" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.03</v>
       </c>
       <c r="N66" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>17 Sep 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Siddhartha Bank Ltd.</t>
+          <t>NIC Asia Bank Limited</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -8215,21 +8233,21 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Ashwin 2083</t>
+          <t>Kartik 2083</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E67" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.0275</v>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H67" s="8" t="n">
@@ -8239,29 +8257,27 @@
         <v>0.0275</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>0.03759999999999999</v>
-      </c>
-      <c r="K67" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="K67" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L67" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M67" s="8" t="n">
-        <v>0.0305</v>
+        <v>0.03</v>
       </c>
       <c r="N67" s="10" t="inlineStr">
         <is>
-          <t>17 Sep 2026</t>
+          <t>1st Kartik 2083 (18th October 2026)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal Ltd.</t>
+          <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -8285,7 +8301,7 @@
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>Up to 0.25%</t>
+          <t>Up to 1.37%</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
@@ -8295,29 +8311,27 @@
         <v>0.0275</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="K68" s="11" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="K68" s="8" t="n">
+        <v>0.0275</v>
       </c>
       <c r="L68" s="8" t="n">
         <v>0.0275</v>
       </c>
       <c r="M68" s="8" t="n">
-        <v>0.0275</v>
+        <v>0.03</v>
       </c>
       <c r="N68" s="10" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>1st Bhadra 2083 (17 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal Ltd.</t>
+          <t>NIC Asia Bank Ltd.</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -8341,37 +8355,1841 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J69" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L69" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M69" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>1st Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>NMB Bank Limited</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I70" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J70" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K70" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L70" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M70" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 1, 2083 (October 18, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>NMB Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I71" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J71" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K71" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L71" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M71" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 1, 2083 (17 Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>NMB Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L72" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M72" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N72" s="10" t="inlineStr">
+        <is>
+          <t>Asoj 1, 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>Nabil Bank Limited</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="K73" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L73" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M73" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>18th October 2026 (1st Kartik 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Nabil Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="K74" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L74" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M74" s="8" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>Nabil Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="J75" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="K75" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L75" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M75" s="8" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1 Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Nepal Bank Limited</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="I76" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="J76" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="K76" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L76" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M76" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>1st Kartik 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Nepal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="K77" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L77" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M77" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N77" s="10" t="inlineStr">
+        <is>
+          <t>1st Bhadra 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Nepal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="J78" s="8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="K78" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L78" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M78" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>1st Ashwin 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.35%</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M79" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.35%</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I80" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J80" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K80" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M80" s="8" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Nepal Investment Mega Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.35%</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J81" s="8" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L81" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M81" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>18th October, 2026 (1st Kartik 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Nepal SBI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.75%</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J82" s="8" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="K82" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L82" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M82" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N82" s="10" t="inlineStr">
+        <is>
+          <t>17 Aug 2026 (1st Bhadra 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Nepal SBI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.75%</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I83" s="8" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J83" s="8" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="K83" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L83" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M83" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N83" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (1st Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Nepal SBI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.35%</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I84" s="8" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J84" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K84" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L84" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M84" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t>18th October 2026 (1st Kartik 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Prabhu Bank Limited</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.10%</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I85" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J85" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="K85" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L85" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M85" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t>October 18, 2026 (01 Kartik 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Prabhu Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.10%</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I86" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J86" s="8" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="K86" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L86" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M86" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>17 Aug 2026 (01 Bhadra 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>Prabhu Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.10%</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I87" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J87" s="8" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="K87" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L87" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M87" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N87" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 (01 Ashwin 2083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I88" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J88" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K88" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L88" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M88" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N88" s="10" t="inlineStr">
+        <is>
+          <t>01st Bhadra 2083 (17 Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I89" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J89" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K89" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L89" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M89" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>01st Ashwin 2083 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Prime Commercial Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.37%</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="I90" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J90" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K90" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L90" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M90" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N90" s="10" t="inlineStr">
+        <is>
+          <t>01st Kartik 2083 (18th October 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Rastriya Banijya Bank Limited</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I91" s="8" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="J91" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K91" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L91" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M91" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>2083 Kartik 01 (18th October 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>Rastriya Banijya Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I92" s="8" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="J92" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K92" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L92" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M92" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N92" s="10" t="inlineStr">
+        <is>
+          <t>2083 Bhadra 01 (17 Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>Rastriya Banijya Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I93" s="8" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="J93" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K93" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L93" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M93" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>2083 Asoj 01 (17 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>Sanima Bank Limited</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I94" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J94" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K94" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L94" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M94" s="8" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="N94" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Sanima Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I95" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J95" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K95" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L95" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M95" s="8" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="N95" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Sanima Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Up to 1.375%</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I96" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="J96" s="8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K96" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="L96" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M96" s="8" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 1, 2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Siddhartha Bank Limited</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>up to 0.25%</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J97" s="8" t="n">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L97" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M97" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="N97" s="10" t="inlineStr">
+        <is>
+          <t>October 18, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>Siddhartha Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.25%</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I98" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J98" s="8" t="n">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="K98" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L98" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M98" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="N98" s="10" t="inlineStr">
+        <is>
+          <t>17 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>Siddhartha Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.25%</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I99" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J99" s="8" t="n">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L99" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M99" s="8" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="N99" s="10" t="inlineStr">
+        <is>
+          <t>17 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Limited</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Kartik 2083</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.15%</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I100" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J100" s="8" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="K100" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L100" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M100" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N100" s="10" t="inlineStr">
+        <is>
+          <t>18th October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Ltd.</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>Bhadra 2083</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>Up to 0.25%</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I101" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J101" s="8" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="L101" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M101" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N101" s="10" t="inlineStr">
+        <is>
+          <t>17 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank Nepal Ltd.</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Commercial Banks</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Ashwin 2083</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="F102" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
           <t>Up to 0.20%</t>
         </is>
       </c>
-      <c r="H69" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="I69" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="J69" s="8" t="n">
+      <c r="H102" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="I102" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="J102" s="8" t="n">
         <v>0.0375</v>
       </c>
-      <c r="K69" s="11" t="inlineStr">
+      <c r="K102" s="11" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L69" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M69" s="8" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="N69" s="10" t="inlineStr">
+      <c r="L102" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M102" s="8" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="N102" s="10" t="inlineStr">
         <is>
           <t>17 Sep 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N69"/>
+  <autoFilter ref="A1:N102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3500,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: LBBL.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3500,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: LBBL.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3500,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: NIMB.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3500,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: NIMB.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: MBL, NIMB.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3500,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: MBL, NIMB.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: MBL, NBL, NICA, NIMB, SADBL.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3500,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: MBL, NBL, NICA, NIMB, SADBL.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: MBL, NIMB.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3500,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: MBL, NIMB.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: GRDBL, LBBL, MBL, NIMB.</t>
         </is>
       </c>
     </row>

--- a/reports/Interest_Rate_Summary.xlsx
+++ b/reports/Interest_Rate_Summary.xlsx
@@ -3500,7 +3500,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: GRDBL, LBBL, MBL, NIMB.</t>
+          <t>Changes = current month minus previous month (percentage points): green = increase, red = decrease, grey = no change, '—' = not comparable. Saving Max = second highest saving rate, excluding the first highest. Newer notices not yet extracted: MBL, NIMB.</t>
         </is>
       </c>
     </row>
